--- a/content/jahrgaenge/Jg7.xlsx
+++ b/content/jahrgaenge/Jg7.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="197">
   <si>
     <t>Hinweise zu Jg7.xlsx</t>
   </si>
@@ -497,14 +497,129 @@
   </si>
   <si>
     <t>Bausteinzeitraum 31.08. bis 02.10.2026</t>
+  </si>
+  <si>
+    <t>sachlich</t>
+  </si>
+  <si>
+    <t>Besinn-Dich-Tage</t>
+  </si>
+  <si>
+    <t>besinntage</t>
+  </si>
+  <si>
+    <t>letzte Schulwoche</t>
+  </si>
+  <si>
+    <t>letzte-woche</t>
+  </si>
+  <si>
+    <t>jg7-bio-1</t>
+  </si>
+  <si>
+    <t>jg7-en-1</t>
+  </si>
+  <si>
+    <t>en</t>
+  </si>
+  <si>
+    <t>jg7-geo-1</t>
+  </si>
+  <si>
+    <t>geo</t>
+  </si>
+  <si>
+    <t>jg7-de-1</t>
+  </si>
+  <si>
+    <t>jg7-ma-1</t>
+  </si>
+  <si>
+    <t>ma</t>
+  </si>
+  <si>
+    <t>jg7-geo-2</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>jg7-bio-2</t>
+  </si>
+  <si>
+    <t>jg7-en-2</t>
+  </si>
+  <si>
+    <t>jg7-de-2</t>
+  </si>
+  <si>
+    <t>jg7-ma-2</t>
+  </si>
+  <si>
+    <t>jg7-en-3</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>jg7-ma-3</t>
+  </si>
+  <si>
+    <t>jg7-bio-3</t>
+  </si>
+  <si>
+    <t>jg7-de-3</t>
+  </si>
+  <si>
+    <t>jg7-geo-3</t>
+  </si>
+  <si>
+    <t>vorlaeufig</t>
+  </si>
+  <si>
+    <t>Geplant ist Geografie. Möglicherweise tauscht dieser Baustein mit Geschichte.</t>
+  </si>
+  <si>
+    <t>jg7-de-4</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>jg7-en-4</t>
+  </si>
+  <si>
+    <t>jg7-bio-4</t>
+  </si>
+  <si>
+    <t>jg7-ma-4</t>
+  </si>
+  <si>
+    <t>jg7-geo-4</t>
+  </si>
+  <si>
+    <t>jg7-fvu-1</t>
+  </si>
+  <si>
+    <t>fvu</t>
+  </si>
+  <si>
+    <t>1,2,3</t>
+  </si>
+  <si>
+    <t>Wie der fächerverbindende Unterricht genau aussieht, steht noch nicht fest.</t>
+  </si>
+  <si>
+    <t>Fächerverbindender Unterricht</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd.mm.yyyy"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -542,7 +657,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -557,6 +672,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1925,7 +2041,7 @@
     <mergeCell ref="B72:D72"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -1956,7 +2072,7 @@
   </sheetData>
   <autoFilter ref="A1:D1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -1992,6 +2108,9 @@
       <c r="A2">
         <v>7</v>
       </c>
+      <c r="B2" t="s">
+        <v>159</v>
+      </c>
       <c r="C2" t="s">
         <v>17</v>
       </c>
@@ -2000,19 +2119,22 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:E1"/>
-  <dataValidations count="1">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" sqref="B10:B500">
+      <formula1>"verspielt,klar,sachlich"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="B2:B500">
       <formula1>"verspielt,klar,sachlich"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="13" style="5" customWidth="1"/>
@@ -2034,21 +2156,66 @@
         <v>34</v>
       </c>
     </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="8">
+        <v>46279</v>
+      </c>
+      <c r="B2" s="8">
+        <v>46283</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="8">
+        <v>46468</v>
+      </c>
+      <c r="B3" s="8">
+        <v>46472</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="8">
+        <v>46573</v>
+      </c>
+      <c r="B4" s="8">
+        <v>46577</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D4" t="s">
+        <v>163</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>
-  <dataValidations count="1">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" sqref="D10:D500">
+      <formula1>"themenwoche,soul-basics,puffer,kennenlernen,einfuehrung,besinntage,fvu,letzte-woche,sonstiges"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="D2:D500">
       <formula1>"themenwoche,soul-basics,puffer,kennenlernen,einfuehrung,besinntage,fvu,letzte-woche,sonstiges"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2099,24 +2266,825 @@
         <v>21</v>
       </c>
     </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2">
+        <v>16</v>
+      </c>
+      <c r="G2" s="8">
+        <v>46251</v>
+      </c>
+      <c r="H2" s="8">
+        <v>46325</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" t="s">
+        <v>164</v>
+      </c>
+      <c r="K2" t="s">
+        <v>65</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3">
+        <v>16</v>
+      </c>
+      <c r="G3" s="8">
+        <v>46251</v>
+      </c>
+      <c r="H3" s="8">
+        <v>46276</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" t="s">
+        <v>165</v>
+      </c>
+      <c r="K3" t="s">
+        <v>65</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4">
+        <v>16</v>
+      </c>
+      <c r="G4" s="8">
+        <v>46251</v>
+      </c>
+      <c r="H4" s="8">
+        <v>46276</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" t="s">
+        <v>167</v>
+      </c>
+      <c r="K4" t="s">
+        <v>65</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5">
+        <v>16</v>
+      </c>
+      <c r="G5" s="8">
+        <v>46286</v>
+      </c>
+      <c r="H5" s="8">
+        <v>46325</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J5" t="s">
+        <v>169</v>
+      </c>
+      <c r="K5" t="s">
+        <v>65</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B6" t="s">
+        <v>171</v>
+      </c>
+      <c r="C6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6">
+        <v>16</v>
+      </c>
+      <c r="G6" s="8">
+        <v>46286</v>
+      </c>
+      <c r="H6" s="8">
+        <v>46325</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J6" t="s">
+        <v>170</v>
+      </c>
+      <c r="K6" t="s">
+        <v>65</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B7" t="s">
+        <v>168</v>
+      </c>
+      <c r="C7" t="s">
+        <v>173</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7">
+        <v>16</v>
+      </c>
+      <c r="G7" s="8">
+        <v>46328</v>
+      </c>
+      <c r="H7" s="8">
+        <v>46395</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J7" t="s">
+        <v>172</v>
+      </c>
+      <c r="K7" t="s">
+        <v>65</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>174</v>
+      </c>
+      <c r="B8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" t="s">
+        <v>173</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8">
+        <v>16</v>
+      </c>
+      <c r="G8" s="8">
+        <v>46328</v>
+      </c>
+      <c r="H8" s="8">
+        <v>46353</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" t="s">
+        <v>174</v>
+      </c>
+      <c r="K8" t="s">
+        <v>65</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>175</v>
+      </c>
+      <c r="B9" t="s">
+        <v>166</v>
+      </c>
+      <c r="C9" t="s">
+        <v>173</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9">
+        <v>16</v>
+      </c>
+      <c r="G9" s="8">
+        <v>46328</v>
+      </c>
+      <c r="H9" s="8">
+        <v>46353</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J9" t="s">
+        <v>175</v>
+      </c>
+      <c r="K9" t="s">
+        <v>65</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>176</v>
+      </c>
+      <c r="B10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" t="s">
+        <v>173</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10">
+        <v>16</v>
+      </c>
+      <c r="G10" s="8">
+        <v>46356</v>
+      </c>
+      <c r="H10" s="8">
+        <v>46395</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J10" t="s">
+        <v>176</v>
+      </c>
+      <c r="K10" t="s">
+        <v>65</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>177</v>
+      </c>
+      <c r="B11" t="s">
+        <v>171</v>
+      </c>
+      <c r="C11" t="s">
+        <v>173</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11">
+        <v>16</v>
+      </c>
+      <c r="G11" s="8">
+        <v>46356</v>
+      </c>
+      <c r="H11" s="8">
+        <v>46395</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J11" t="s">
+        <v>177</v>
+      </c>
+      <c r="K11" t="s">
+        <v>65</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>178</v>
+      </c>
+      <c r="B12" t="s">
+        <v>166</v>
+      </c>
+      <c r="C12" t="s">
+        <v>179</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12">
+        <v>16</v>
+      </c>
+      <c r="G12" s="8">
+        <v>46398</v>
+      </c>
+      <c r="H12" s="8">
+        <v>46465</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" t="s">
+        <v>178</v>
+      </c>
+      <c r="K12" t="s">
+        <v>65</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>180</v>
+      </c>
+      <c r="B13" t="s">
+        <v>171</v>
+      </c>
+      <c r="C13" t="s">
+        <v>179</v>
+      </c>
+      <c r="D13">
+        <v>2</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13">
+        <v>16</v>
+      </c>
+      <c r="G13" s="8">
+        <v>46398</v>
+      </c>
+      <c r="H13" s="8">
+        <v>46423</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J13" t="s">
+        <v>180</v>
+      </c>
+      <c r="K13" t="s">
+        <v>65</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>181</v>
+      </c>
+      <c r="B14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" t="s">
+        <v>179</v>
+      </c>
+      <c r="D14">
+        <v>3</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14">
+        <v>16</v>
+      </c>
+      <c r="G14" s="8">
+        <v>46398</v>
+      </c>
+      <c r="H14" s="8">
+        <v>46423</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" t="s">
+        <v>181</v>
+      </c>
+      <c r="K14" t="s">
+        <v>65</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>182</v>
+      </c>
+      <c r="B15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" t="s">
+        <v>179</v>
+      </c>
+      <c r="D15">
+        <v>2</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15">
+        <v>16</v>
+      </c>
+      <c r="G15" s="8">
+        <v>46440</v>
+      </c>
+      <c r="H15" s="8">
+        <v>46465</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" t="s">
+        <v>182</v>
+      </c>
+      <c r="K15" t="s">
+        <v>65</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>183</v>
+      </c>
+      <c r="B16" t="s">
+        <v>168</v>
+      </c>
+      <c r="C16" t="s">
+        <v>179</v>
+      </c>
+      <c r="D16">
+        <v>3</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16">
+        <v>16</v>
+      </c>
+      <c r="G16" s="8">
+        <v>46440</v>
+      </c>
+      <c r="H16" s="8">
+        <v>46465</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J16" t="s">
+        <v>183</v>
+      </c>
+      <c r="K16" t="s">
+        <v>184</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>186</v>
+      </c>
+      <c r="B17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" t="s">
+        <v>187</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17">
+        <v>16</v>
+      </c>
+      <c r="G17" s="8">
+        <v>46482</v>
+      </c>
+      <c r="H17" s="8">
+        <v>46542</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" t="s">
+        <v>186</v>
+      </c>
+      <c r="K17" t="s">
+        <v>65</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>188</v>
+      </c>
+      <c r="B18" t="s">
+        <v>166</v>
+      </c>
+      <c r="C18" t="s">
+        <v>187</v>
+      </c>
+      <c r="D18">
+        <v>2</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18">
+        <v>16</v>
+      </c>
+      <c r="G18" s="8">
+        <v>46482</v>
+      </c>
+      <c r="H18" s="8">
+        <v>46507</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" t="s">
+        <v>188</v>
+      </c>
+      <c r="K18" t="s">
+        <v>65</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>189</v>
+      </c>
+      <c r="B19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" t="s">
+        <v>187</v>
+      </c>
+      <c r="D19">
+        <v>3</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19">
+        <v>16</v>
+      </c>
+      <c r="G19" s="8">
+        <v>46482</v>
+      </c>
+      <c r="H19" s="8">
+        <v>46507</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J19" t="s">
+        <v>189</v>
+      </c>
+      <c r="K19" t="s">
+        <v>65</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>190</v>
+      </c>
+      <c r="B20" t="s">
+        <v>171</v>
+      </c>
+      <c r="C20" t="s">
+        <v>187</v>
+      </c>
+      <c r="D20">
+        <v>2</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20">
+        <v>16</v>
+      </c>
+      <c r="G20" s="8">
+        <v>46510</v>
+      </c>
+      <c r="H20" s="8">
+        <v>46542</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" t="s">
+        <v>190</v>
+      </c>
+      <c r="K20" t="s">
+        <v>65</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>191</v>
+      </c>
+      <c r="B21" t="s">
+        <v>168</v>
+      </c>
+      <c r="C21" t="s">
+        <v>187</v>
+      </c>
+      <c r="D21">
+        <v>3</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21">
+        <v>16</v>
+      </c>
+      <c r="G21" s="8">
+        <v>46510</v>
+      </c>
+      <c r="H21" s="8">
+        <v>46542</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" t="s">
+        <v>191</v>
+      </c>
+      <c r="K21" t="s">
+        <v>184</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>192</v>
+      </c>
+      <c r="B22" t="s">
+        <v>193</v>
+      </c>
+      <c r="C22" t="s">
+        <v>47</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22" t="s">
+        <v>194</v>
+      </c>
+      <c r="G22" s="8">
+        <v>46545</v>
+      </c>
+      <c r="H22" s="8">
+        <v>46570</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" t="s">
+        <v>192</v>
+      </c>
+      <c r="K22" t="s">
+        <v>65</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L1"/>
-  <dataValidations count="2">
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" sqref="B10:B500">
+      <formula1>"de,ma,en,bio,geo,fvu,offen"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="B2:B500">
       <formula1>"de,ma,en,bio,geo,fvu,offen"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="K10:K500">
+      <formula1>"fest,wahl,vorlaeufig,offen"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="K2:K500">
       <formula1>"fest,wahl,vorlaeufig,offen"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2155,15 +3123,564 @@
         <v>85</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B6" t="s">
+        <v>171</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B7" t="s">
+        <v>168</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>174</v>
+      </c>
+      <c r="B8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>175</v>
+      </c>
+      <c r="B9" t="s">
+        <v>166</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>176</v>
+      </c>
+      <c r="B10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>177</v>
+      </c>
+      <c r="B11" t="s">
+        <v>171</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>8</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>178</v>
+      </c>
+      <c r="B12" t="s">
+        <v>166</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>180</v>
+      </c>
+      <c r="B13" t="s">
+        <v>171</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>8</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>181</v>
+      </c>
+      <c r="B14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>182</v>
+      </c>
+      <c r="B15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>183</v>
+      </c>
+      <c r="B16" t="s">
+        <v>168</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>8</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>186</v>
+      </c>
+      <c r="B17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>188</v>
+      </c>
+      <c r="B18" t="s">
+        <v>166</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>189</v>
+      </c>
+      <c r="B19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>8</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>190</v>
+      </c>
+      <c r="B20" t="s">
+        <v>171</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>191</v>
+      </c>
+      <c r="B21" t="s">
+        <v>168</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>192</v>
+      </c>
+      <c r="B22" t="s">
+        <v>193</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
-  <dataValidations count="1">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" sqref="B10:B500">
+      <formula1>"de,ma,en,bio,geo,fvu,offen"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="B2:B500">
       <formula1>"de,ma,en,bio,geo,fvu,offen"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -2208,13 +3725,16 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
-  <dataValidations count="1">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" sqref="D10:D500">
+      <formula1>"pflicht,wahl"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="D2:D500">
       <formula1>"pflicht,wahl"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -2255,19 +3775,28 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:G1"/>
-  <dataValidations count="3">
+  <dataValidations count="6">
+    <dataValidation type="list" allowBlank="1" sqref="B10:B500">
+      <formula1>"de,ma,en,bio,geo,fvu,offen"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="B2:B500">
       <formula1>"de,ma,en,bio,geo,fvu,offen"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C10:C500">
+      <formula1>"fach,methode,baustein"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="C2:C500">
       <formula1>"fach,methode,baustein"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="F10:F500">
+      <formula1>"ja,nein"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="F2:F500">
       <formula1>"ja,nein"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -2300,16 +3829,22 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:E1"/>
-  <dataValidations count="2">
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" sqref="A10:A500">
+      <formula1>"Mo,Di,Mi,Do,Fr"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="A2:A500">
       <formula1>"Mo,Di,Mi,Do,Fr"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="E10:E500">
+      <formula1>"A,B,C"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="E2:E500">
       <formula1>"A,B,C"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -2361,21 +3896,33 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
-  <dataValidations count="4">
+  <dataValidations count="8">
+    <dataValidation type="list" allowBlank="1" sqref="B10:B500">
+      <formula1>"input,coaching,sonstiges,entfall"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="B2:B500">
       <formula1>"input,coaching,sonstiges,entfall"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C10:C500">
+      <formula1>"de,ma,en,bio,geo,fvu,offen"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="C2:C500">
       <formula1>"de,ma,en,bio,geo,fvu,offen"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="E10:E500">
+      <formula1>"A,B,C"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="E2:E500">
       <formula1>"A,B,C"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="I10:I500">
+      <formula1>"ja,nein"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="I2:I500">
       <formula1>"ja,nein"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/content/jahrgaenge/Jg7.xlsx
+++ b/content/jahrgaenge/Jg7.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="278">
   <si>
     <t>Hinweise zu Jg7.xlsx</t>
   </si>
@@ -610,7 +610,250 @@
     <t>Wie der fächerverbindende Unterricht genau aussieht, steht noch nicht fest.</t>
   </si>
   <si>
+    <t>Krankheitserreger und Immunsystem</t>
+  </si>
+  <si>
+    <t>Fallbericht an das Gesundheitsamt</t>
+  </si>
+  <si>
+    <t>Die geheimnisvolle Welt der Balladen</t>
+  </si>
+  <si>
+    <t>komplexe Leistung</t>
+  </si>
+  <si>
+    <t>Prozent- und Zinsrechnung</t>
+  </si>
+  <si>
+    <t>Prozent- und Zinsaufgaben sicher lösen und das Vorgehen erklären</t>
+  </si>
+  <si>
     <t>Fächerverbindender Unterricht</t>
+  </si>
+  <si>
+    <t>Vorwissen: Anteile und Prozente</t>
+  </si>
+  <si>
+    <t>Heft, M1, Lehrbuch</t>
+  </si>
+  <si>
+    <t>Grundbegriffe der Prozentrechnung</t>
+  </si>
+  <si>
+    <t>1. Grundaufgabe: Prozentsatz</t>
+  </si>
+  <si>
+    <t>Heft, M2, Lehrbuch</t>
+  </si>
+  <si>
+    <t>2. Grundaufgabe: Prozentwert</t>
+  </si>
+  <si>
+    <t>3. Grundaufgabe: Grundwert</t>
+  </si>
+  <si>
+    <t>Übung: Die drei Grundaufgaben</t>
+  </si>
+  <si>
+    <t>wahl</t>
+  </si>
+  <si>
+    <t>Für Gymnasiasten ab Jgst. 7 Pflicht.</t>
+  </si>
+  <si>
+    <t>Diagramme und Prozente</t>
+  </si>
+  <si>
+    <t>Heft, Geodreieck, Zirkel, Lehrbuch</t>
+  </si>
+  <si>
+    <t>Anwendung: Rabatt und Preisnachlass</t>
+  </si>
+  <si>
+    <t>Mehrwertsteuer und Brutto / Netto</t>
+  </si>
+  <si>
+    <t>Prozentuale Zunahme und Abnahme</t>
+  </si>
+  <si>
+    <t>Zinsrechnung: Jahreszinsen</t>
+  </si>
+  <si>
+    <t>Heft, M3</t>
+  </si>
+  <si>
+    <t>Zinsrechnung: Monats- &amp; Tageszinsen</t>
+  </si>
+  <si>
+    <t>Gelingensnachweis</t>
+  </si>
+  <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>Der Ausbruch beginnt (OS/GYM)</t>
+  </si>
+  <si>
+    <t>iPad, Website</t>
+  </si>
+  <si>
+    <t>Die unsichtbaren Verdächtigen – Bakterien und Viren (OS/GYM)</t>
+  </si>
+  <si>
+    <t>A1, iPad, Website</t>
+  </si>
+  <si>
+    <t>Bakterien unter der Lupe</t>
+  </si>
+  <si>
+    <t>A2, iPad, Website</t>
+  </si>
+  <si>
+    <t>Viren – Leben an der Grenze</t>
+  </si>
+  <si>
+    <t>Die Kette der Ansteckung (OS/GYM)</t>
+  </si>
+  <si>
+    <t>A3, iPad, Website</t>
+  </si>
+  <si>
+    <t>Das Einsatzteam im Blut (OS/GYM)</t>
+  </si>
+  <si>
+    <t>A4 oder A5, iPad, Website</t>
+  </si>
+  <si>
+    <t>Die Abwehr schlägt zurück (OS/GYM)</t>
+  </si>
+  <si>
+    <t>A6, iPad, Website</t>
+  </si>
+  <si>
+    <t>Wenn aus einem viele werden</t>
+  </si>
+  <si>
+    <t>Warum wird man krank (OS/GYM)</t>
+  </si>
+  <si>
+    <t>A7 oder A8, iPad, Website</t>
+  </si>
+  <si>
+    <t>Training für die Abwehr (OS/GYM)</t>
+  </si>
+  <si>
+    <t>Die Detektive der Wissenschaft</t>
+  </si>
+  <si>
+    <t>Fallbericht an das Gesundheitsamt (OS/GYM)</t>
+  </si>
+  <si>
+    <t>iPad, Website, Aktendulli</t>
+  </si>
+  <si>
+    <t>Wenn Gerüchte krank machen</t>
+  </si>
+  <si>
+    <t>Gesund handeln im Alltag</t>
+  </si>
+  <si>
+    <t>A9, iPad, Website</t>
+  </si>
+  <si>
+    <t>Lyrik-Check</t>
+  </si>
+  <si>
+    <t>iPad</t>
+  </si>
+  <si>
+    <t>Unbekannte Spurensuche</t>
+  </si>
+  <si>
+    <t>Hefter, A1, A2</t>
+  </si>
+  <si>
+    <t>Die Geheimformel der Balladen (3a)</t>
+  </si>
+  <si>
+    <t>A3, M1, M2, Hefter, iPad</t>
+  </si>
+  <si>
+    <t>Anwendung der Geheimformel (3b)</t>
+  </si>
+  <si>
+    <t>A4</t>
+  </si>
+  <si>
+    <t>Balladen inhaltlich verstehen (4a)</t>
+  </si>
+  <si>
+    <t>A5, iPad</t>
+  </si>
+  <si>
+    <t>Balladen am roten Faden (4b)</t>
+  </si>
+  <si>
+    <t>M3, M4, Papier, Briefumschlag, Faden</t>
+  </si>
+  <si>
+    <t>Wahrheitssuche in einer Ballade</t>
+  </si>
+  <si>
+    <t>Hefter, A6</t>
+  </si>
+  <si>
+    <t>Der Konjunktiv-Check</t>
+  </si>
+  <si>
+    <t>M5, A7</t>
+  </si>
+  <si>
+    <t>Sprache mit Stil – Nachrichten im Konjunktiv</t>
+  </si>
+  <si>
+    <t>Hefter, A8</t>
+  </si>
+  <si>
+    <t>Eine Ballade unter der Lupe</t>
+  </si>
+  <si>
+    <t>A9, M6, iPad</t>
+  </si>
+  <si>
+    <t>Sprachliche Stilmittel in Balladen</t>
+  </si>
+  <si>
+    <t>Wenn Worte Bilder zaubern</t>
+  </si>
+  <si>
+    <t>iPad, A10</t>
+  </si>
+  <si>
+    <t>Das Zauberchaos</t>
+  </si>
+  <si>
+    <t>M7</t>
+  </si>
+  <si>
+    <t>Zwei Perspektiven, ein Schicksal</t>
+  </si>
+  <si>
+    <t>A11, A12, M8</t>
+  </si>
+  <si>
+    <t>Bühne frei</t>
+  </si>
+  <si>
+    <t>M9</t>
+  </si>
+  <si>
+    <t>Eine Ballade zum Leben erwecken</t>
+  </si>
+  <si>
+    <t>Link / QR-Code</t>
+  </si>
+  <si>
+    <t>Läuft über 2 Termine à 90 Minuten.</t>
   </si>
 </sst>
 </file>
@@ -3131,16 +3374,16 @@
         <v>72</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>196</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>8</v>
+        <v>197</v>
+      </c>
+      <c r="F2">
+        <v>12</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>8</v>
@@ -3209,13 +3452,13 @@
         <v>44</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>8</v>
+        <v>198</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>8</v>
+        <v>199</v>
       </c>
       <c r="F5" t="s">
         <v>8</v>
@@ -3235,16 +3478,16 @@
         <v>171</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>8</v>
+        <v>200</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>8</v>
+        <v>201</v>
+      </c>
+      <c r="F6">
+        <v>13</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>8</v>
@@ -3651,7 +3894,7 @@
         <v>193</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>8</v>
@@ -3686,7 +3929,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3721,6 +3964,1124 @@
       </c>
       <c r="H1" s="7" t="s">
         <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E2">
+        <v>45</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E3">
+        <v>45</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E4">
+        <v>90</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E5">
+        <v>90</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6">
+        <v>90</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>170</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D7" t="s">
+        <v>211</v>
+      </c>
+      <c r="E7">
+        <v>90</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>170</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D8" t="s">
+        <v>93</v>
+      </c>
+      <c r="E8">
+        <v>45</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>170</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D9" t="s">
+        <v>211</v>
+      </c>
+      <c r="E9">
+        <v>90</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>170</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D10" t="s">
+        <v>93</v>
+      </c>
+      <c r="E10">
+        <v>90</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>170</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D11" t="s">
+        <v>93</v>
+      </c>
+      <c r="E11">
+        <v>45</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>170</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D12" t="s">
+        <v>93</v>
+      </c>
+      <c r="E12">
+        <v>90</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>170</v>
+      </c>
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D13" t="s">
+        <v>211</v>
+      </c>
+      <c r="E13">
+        <v>60</v>
+      </c>
+      <c r="F13">
+        <v>3</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>170</v>
+      </c>
+      <c r="B14">
+        <v>13</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D14" t="s">
+        <v>93</v>
+      </c>
+      <c r="E14">
+        <v>90</v>
+      </c>
+      <c r="F14">
+        <v>3</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>164</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D15" t="s">
+        <v>93</v>
+      </c>
+      <c r="E15">
+        <v>40</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>164</v>
+      </c>
+      <c r="B16">
+        <v>2</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D16" t="s">
+        <v>93</v>
+      </c>
+      <c r="E16">
+        <v>40</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>164</v>
+      </c>
+      <c r="B17">
+        <v>3</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D17" t="s">
+        <v>211</v>
+      </c>
+      <c r="E17">
+        <v>40</v>
+      </c>
+      <c r="F17">
+        <v>3</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>164</v>
+      </c>
+      <c r="B18">
+        <v>4</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D18" t="s">
+        <v>211</v>
+      </c>
+      <c r="E18">
+        <v>40</v>
+      </c>
+      <c r="F18">
+        <v>3</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>164</v>
+      </c>
+      <c r="B19">
+        <v>5</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D19" t="s">
+        <v>93</v>
+      </c>
+      <c r="E19">
+        <v>50</v>
+      </c>
+      <c r="F19">
+        <v>3</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>164</v>
+      </c>
+      <c r="B20">
+        <v>6</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D20" t="s">
+        <v>93</v>
+      </c>
+      <c r="E20">
+        <v>60</v>
+      </c>
+      <c r="F20">
+        <v>3</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>164</v>
+      </c>
+      <c r="B21">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D21" t="s">
+        <v>93</v>
+      </c>
+      <c r="E21">
+        <v>50</v>
+      </c>
+      <c r="F21">
+        <v>2</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>164</v>
+      </c>
+      <c r="B22">
+        <v>8</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D22" t="s">
+        <v>211</v>
+      </c>
+      <c r="E22">
+        <v>40</v>
+      </c>
+      <c r="F22">
+        <v>2</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>164</v>
+      </c>
+      <c r="B23">
+        <v>9</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D23" t="s">
+        <v>93</v>
+      </c>
+      <c r="E23">
+        <v>30</v>
+      </c>
+      <c r="F23">
+        <v>3</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>164</v>
+      </c>
+      <c r="B24">
+        <v>10</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D24" t="s">
+        <v>93</v>
+      </c>
+      <c r="E24">
+        <v>30</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>164</v>
+      </c>
+      <c r="B25">
+        <v>11</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D25" t="s">
+        <v>211</v>
+      </c>
+      <c r="E25">
+        <v>40</v>
+      </c>
+      <c r="F25">
+        <v>3</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>164</v>
+      </c>
+      <c r="B26">
+        <v>12</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D26" t="s">
+        <v>93</v>
+      </c>
+      <c r="E26">
+        <v>100</v>
+      </c>
+      <c r="F26">
+        <v>3</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>164</v>
+      </c>
+      <c r="B27">
+        <v>13</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D27" t="s">
+        <v>211</v>
+      </c>
+      <c r="E27">
+        <v>30</v>
+      </c>
+      <c r="F27">
+        <v>2</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>164</v>
+      </c>
+      <c r="B28">
+        <v>14</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="D28" t="s">
+        <v>211</v>
+      </c>
+      <c r="E28">
+        <v>30</v>
+      </c>
+      <c r="F28">
+        <v>2</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>169</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D29" t="s">
+        <v>211</v>
+      </c>
+      <c r="E29">
+        <v>10</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>169</v>
+      </c>
+      <c r="B30">
+        <v>2</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D30" t="s">
+        <v>93</v>
+      </c>
+      <c r="E30">
+        <v>25</v>
+      </c>
+      <c r="F30">
+        <v>2</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>169</v>
+      </c>
+      <c r="B31">
+        <v>3</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D31" t="s">
+        <v>93</v>
+      </c>
+      <c r="E31">
+        <v>45</v>
+      </c>
+      <c r="F31">
+        <v>2</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>169</v>
+      </c>
+      <c r="B32">
+        <v>4</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D32" t="s">
+        <v>93</v>
+      </c>
+      <c r="E32">
+        <v>45</v>
+      </c>
+      <c r="F32">
+        <v>3</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>169</v>
+      </c>
+      <c r="B33">
+        <v>5</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="D33" t="s">
+        <v>93</v>
+      </c>
+      <c r="E33">
+        <v>15</v>
+      </c>
+      <c r="F33">
+        <v>2</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>169</v>
+      </c>
+      <c r="B34">
+        <v>6</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D34" t="s">
+        <v>93</v>
+      </c>
+      <c r="E34">
+        <v>60</v>
+      </c>
+      <c r="F34">
+        <v>3</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>169</v>
+      </c>
+      <c r="B35">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D35" t="s">
+        <v>93</v>
+      </c>
+      <c r="E35">
+        <v>20</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>169</v>
+      </c>
+      <c r="B36">
+        <v>8</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D36" t="s">
+        <v>211</v>
+      </c>
+      <c r="E36">
+        <v>15</v>
+      </c>
+      <c r="F36">
+        <v>1</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>169</v>
+      </c>
+      <c r="B37">
+        <v>9</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D37" t="s">
+        <v>93</v>
+      </c>
+      <c r="E37">
+        <v>30</v>
+      </c>
+      <c r="F37">
+        <v>3</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>169</v>
+      </c>
+      <c r="B38">
+        <v>10</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D38" t="s">
+        <v>93</v>
+      </c>
+      <c r="E38">
+        <v>35</v>
+      </c>
+      <c r="F38">
+        <v>2</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>169</v>
+      </c>
+      <c r="B39">
+        <v>11</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D39" t="s">
+        <v>211</v>
+      </c>
+      <c r="E39">
+        <v>10</v>
+      </c>
+      <c r="F39">
+        <v>1</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>169</v>
+      </c>
+      <c r="B40">
+        <v>12</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="D40" t="s">
+        <v>93</v>
+      </c>
+      <c r="E40">
+        <v>25</v>
+      </c>
+      <c r="F40">
+        <v>2</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>169</v>
+      </c>
+      <c r="B41">
+        <v>13</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="D41" t="s">
+        <v>211</v>
+      </c>
+      <c r="E41">
+        <v>10</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>169</v>
+      </c>
+      <c r="B42">
+        <v>14</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="D42" t="s">
+        <v>93</v>
+      </c>
+      <c r="E42">
+        <v>35</v>
+      </c>
+      <c r="F42">
+        <v>2</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>169</v>
+      </c>
+      <c r="B43">
+        <v>15</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D43" t="s">
+        <v>211</v>
+      </c>
+      <c r="E43">
+        <v>45</v>
+      </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>169</v>
+      </c>
+      <c r="B44">
+        <v>16</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="D44" t="s">
+        <v>93</v>
+      </c>
+      <c r="E44">
+        <v>90</v>
+      </c>
+      <c r="F44">
+        <v>3</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>277</v>
       </c>
     </row>
   </sheetData>

--- a/content/jahrgaenge/Jg7.xlsx
+++ b/content/jahrgaenge/Jg7.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="305">
   <si>
     <t>Hinweise zu Jg7.xlsx</t>
   </si>
@@ -854,6 +854,87 @@
   </si>
   <si>
     <t>Läuft über 2 Termine à 90 Minuten.</t>
+  </si>
+  <si>
+    <t>2026-09-21</t>
+  </si>
+  <si>
+    <t>coaching</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>2026-09-25</t>
+  </si>
+  <si>
+    <t>HEI</t>
+  </si>
+  <si>
+    <t>2026-09-28</t>
+  </si>
+  <si>
+    <t>2026-09-29</t>
+  </si>
+  <si>
+    <t>STE</t>
+  </si>
+  <si>
+    <t>2026-09-30</t>
+  </si>
+  <si>
+    <t>2026-10-01</t>
+  </si>
+  <si>
+    <t>DUB</t>
+  </si>
+  <si>
+    <t>SMT</t>
+  </si>
+  <si>
+    <t>Spezifische Immunabwehr – Antikörper und Gedächtniszellen</t>
+  </si>
+  <si>
+    <t>BAL</t>
+  </si>
+  <si>
+    <t>2026-10-05</t>
+  </si>
+  <si>
+    <t>2026-10-06</t>
+  </si>
+  <si>
+    <t>2026-10-07</t>
+  </si>
+  <si>
+    <t>2026-10-08</t>
+  </si>
+  <si>
+    <t>2026-10-09</t>
+  </si>
+  <si>
+    <t>Krankheitsverlauf, Fieber und Schutzimpfung</t>
+  </si>
+  <si>
+    <t>sonstiges</t>
+  </si>
+  <si>
+    <t>Pädagogischer Tag – Heimarbeit</t>
+  </si>
+  <si>
+    <t>2026-10-27</t>
+  </si>
+  <si>
+    <t>2026-10-28</t>
+  </si>
+  <si>
+    <t>2026-10-29</t>
+  </si>
+  <si>
+    <t>2026-10-30</t>
+  </si>
+  <si>
+    <t>Antibiotika – Wirkung, richtige Anwendung und Resistenzen</t>
   </si>
 </sst>
 </file>
@@ -5211,7 +5292,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="13" style="5" customWidth="1"/>
@@ -5253,6 +5334,710 @@
       </c>
       <c r="J1" s="3" t="s">
         <v>149</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="B2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="B3" t="s">
+        <v>279</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>282</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="B4" t="s">
+        <v>279</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" t="s">
+        <v>280</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="B5" t="s">
+        <v>138</v>
+      </c>
+      <c r="C5" t="s">
+        <v>171</v>
+      </c>
+      <c r="D5" t="s">
+        <v>285</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5" t="s">
+        <v>8</v>
+      </c>
+      <c r="I5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="B6" t="s">
+        <v>279</v>
+      </c>
+      <c r="C6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" t="s">
+        <v>282</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" t="s">
+        <v>8</v>
+      </c>
+      <c r="I6" t="s">
+        <v>8</v>
+      </c>
+      <c r="J6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="B7" t="s">
+        <v>138</v>
+      </c>
+      <c r="C7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" t="s">
+        <v>288</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" t="s">
+        <v>8</v>
+      </c>
+      <c r="I7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="B8" t="s">
+        <v>279</v>
+      </c>
+      <c r="C8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" t="s">
+        <v>289</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H8" t="s">
+        <v>8</v>
+      </c>
+      <c r="I8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" t="s">
+        <v>138</v>
+      </c>
+      <c r="C9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" t="s">
+        <v>140</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="H9" t="s">
+        <v>8</v>
+      </c>
+      <c r="I9" t="s">
+        <v>8</v>
+      </c>
+      <c r="J9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" t="s">
+        <v>279</v>
+      </c>
+      <c r="C10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" t="s">
+        <v>291</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H10" t="s">
+        <v>8</v>
+      </c>
+      <c r="I10" t="s">
+        <v>8</v>
+      </c>
+      <c r="J10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="B11" t="s">
+        <v>279</v>
+      </c>
+      <c r="C11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" t="s">
+        <v>280</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>8</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H11" t="s">
+        <v>8</v>
+      </c>
+      <c r="I11" t="s">
+        <v>8</v>
+      </c>
+      <c r="J11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="B12" t="s">
+        <v>138</v>
+      </c>
+      <c r="C12" t="s">
+        <v>171</v>
+      </c>
+      <c r="D12" t="s">
+        <v>285</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="B13" t="s">
+        <v>279</v>
+      </c>
+      <c r="C13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" t="s">
+        <v>280</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>8</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H13" t="s">
+        <v>8</v>
+      </c>
+      <c r="I13" t="s">
+        <v>8</v>
+      </c>
+      <c r="J13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="B14" t="s">
+        <v>138</v>
+      </c>
+      <c r="C14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" t="s">
+        <v>288</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="B15" t="s">
+        <v>279</v>
+      </c>
+      <c r="C15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" t="s">
+        <v>289</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H15" t="s">
+        <v>8</v>
+      </c>
+      <c r="I15" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="B16" t="s">
+        <v>138</v>
+      </c>
+      <c r="C16" t="s">
+        <v>72</v>
+      </c>
+      <c r="D16" t="s">
+        <v>140</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>8</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="H16" t="s">
+        <v>8</v>
+      </c>
+      <c r="I16" t="s">
+        <v>8</v>
+      </c>
+      <c r="J16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="B17" t="s">
+        <v>279</v>
+      </c>
+      <c r="C17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" t="s">
+        <v>291</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" t="s">
+        <v>298</v>
+      </c>
+      <c r="C18" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="H18" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="B19" t="s">
+        <v>138</v>
+      </c>
+      <c r="C19" t="s">
+        <v>171</v>
+      </c>
+      <c r="D19" t="s">
+        <v>285</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>8</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H19" t="s">
+        <v>8</v>
+      </c>
+      <c r="I19" t="s">
+        <v>8</v>
+      </c>
+      <c r="J19" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="B20" t="s">
+        <v>279</v>
+      </c>
+      <c r="C20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" t="s">
+        <v>280</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="B21" t="s">
+        <v>138</v>
+      </c>
+      <c r="C21" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" t="s">
+        <v>288</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H21" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="B22" t="s">
+        <v>279</v>
+      </c>
+      <c r="C22" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" t="s">
+        <v>289</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="B23" t="s">
+        <v>138</v>
+      </c>
+      <c r="C23" t="s">
+        <v>72</v>
+      </c>
+      <c r="D23" t="s">
+        <v>140</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="H23" t="s">
+        <v>8</v>
+      </c>
+      <c r="I23" t="s">
+        <v>8</v>
+      </c>
+      <c r="J23" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/content/jahrgaenge/Jg7.xlsx
+++ b/content/jahrgaenge/Jg7.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1964" uniqueCount="386">
   <si>
     <t>Hinweise zu Jg7.xlsx</t>
   </si>
@@ -856,21 +856,96 @@
     <t>Läuft über 2 Termine à 90 Minuten.</t>
   </si>
   <si>
+    <t>2026-08-24</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>Koordinaten ablesen</t>
+  </si>
+  <si>
+    <t>coaching</t>
+  </si>
+  <si>
+    <t>HIL</t>
+  </si>
+  <si>
+    <t>2026-08-25</t>
+  </si>
+  <si>
+    <t>DUB</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>HEI</t>
+  </si>
+  <si>
+    <t>How to describe a picture using Present Progressive (Station 9-11)</t>
+  </si>
+  <si>
+    <t>BAL</t>
+  </si>
+  <si>
+    <t>2026-08-27</t>
+  </si>
+  <si>
+    <t>SMT</t>
+  </si>
+  <si>
+    <t>2026-08-28</t>
+  </si>
+  <si>
+    <t>Bakterien und Viren – Aufbau, Unterschiede und Vermehrung</t>
+  </si>
+  <si>
+    <t>Beleuchtungszonen / Jahreszeiten</t>
+  </si>
+  <si>
+    <t>2026-09-01</t>
+  </si>
+  <si>
+    <t>2026-09-02</t>
+  </si>
+  <si>
+    <t>How to write a character profile using the present tense</t>
+  </si>
+  <si>
+    <t>2026-09-03</t>
+  </si>
+  <si>
+    <t>2026-09-04</t>
+  </si>
+  <si>
+    <t>Ansteckung – So werden Krankheitserreger übertragen</t>
+  </si>
+  <si>
+    <t>Klimazonen / Klimadiagramme</t>
+  </si>
+  <si>
+    <t>2026-09-09</t>
+  </si>
+  <si>
+    <t>How to write a diary entry using Simple Past</t>
+  </si>
+  <si>
+    <t>2026-09-10</t>
+  </si>
+  <si>
+    <t>2026-09-11</t>
+  </si>
+  <si>
+    <t>Schutzbarrieren und unspezifische Immunabwehr</t>
+  </si>
+  <si>
     <t>2026-09-21</t>
   </si>
   <si>
-    <t>coaching</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
     <t>2026-09-25</t>
   </si>
   <si>
-    <t>HEI</t>
-  </si>
-  <si>
     <t>2026-09-28</t>
   </si>
   <si>
@@ -886,18 +961,9 @@
     <t>2026-10-01</t>
   </si>
   <si>
-    <t>DUB</t>
-  </si>
-  <si>
-    <t>SMT</t>
-  </si>
-  <si>
     <t>Spezifische Immunabwehr – Antikörper und Gedächtniszellen</t>
   </si>
   <si>
-    <t>BAL</t>
-  </si>
-  <si>
     <t>2026-10-05</t>
   </si>
   <si>
@@ -935,6 +1001,183 @@
   </si>
   <si>
     <t>Antibiotika – Wirkung, richtige Anwendung und Resistenzen</t>
+  </si>
+  <si>
+    <t>2026-11-04</t>
+  </si>
+  <si>
+    <t>2026-11-05</t>
+  </si>
+  <si>
+    <t>2026-11-09</t>
+  </si>
+  <si>
+    <t>2026-11-10</t>
+  </si>
+  <si>
+    <t>2026-11-11</t>
+  </si>
+  <si>
+    <t>2026-11-12</t>
+  </si>
+  <si>
+    <t>2026-11-13</t>
+  </si>
+  <si>
+    <t>2026-11-16</t>
+  </si>
+  <si>
+    <t>2026-11-17</t>
+  </si>
+  <si>
+    <t>2026-11-19</t>
+  </si>
+  <si>
+    <t>2026-11-20</t>
+  </si>
+  <si>
+    <t>2026-11-23</t>
+  </si>
+  <si>
+    <t>2026-11-24</t>
+  </si>
+  <si>
+    <t>2026-11-27</t>
+  </si>
+  <si>
+    <t>2026-12-08</t>
+  </si>
+  <si>
+    <t>2026-12-09</t>
+  </si>
+  <si>
+    <t>2026-12-10</t>
+  </si>
+  <si>
+    <t>2026-12-15</t>
+  </si>
+  <si>
+    <t>2026-12-16</t>
+  </si>
+  <si>
+    <t>2026-12-17</t>
+  </si>
+  <si>
+    <t>2027-01-05</t>
+  </si>
+  <si>
+    <t>2027-01-06</t>
+  </si>
+  <si>
+    <t>2027-01-07</t>
+  </si>
+  <si>
+    <t>2027-01-19</t>
+  </si>
+  <si>
+    <t>2027-01-20</t>
+  </si>
+  <si>
+    <t>2027-01-22</t>
+  </si>
+  <si>
+    <t>BRU</t>
+  </si>
+  <si>
+    <t>2027-01-25</t>
+  </si>
+  <si>
+    <t>2027-01-26</t>
+  </si>
+  <si>
+    <t>2027-01-27</t>
+  </si>
+  <si>
+    <t>2027-01-29</t>
+  </si>
+  <si>
+    <t>2027-02-02</t>
+  </si>
+  <si>
+    <t>2027-02-03</t>
+  </si>
+  <si>
+    <t>2027-02-05</t>
+  </si>
+  <si>
+    <t>2027-03-02</t>
+  </si>
+  <si>
+    <t>2027-03-04</t>
+  </si>
+  <si>
+    <t>2027-03-09</t>
+  </si>
+  <si>
+    <t>2027-03-11</t>
+  </si>
+  <si>
+    <t>2027-03-16</t>
+  </si>
+  <si>
+    <t>2027-03-18</t>
+  </si>
+  <si>
+    <t>2027-04-12</t>
+  </si>
+  <si>
+    <t>2027-04-13</t>
+  </si>
+  <si>
+    <t>2027-04-14</t>
+  </si>
+  <si>
+    <t>2027-04-15</t>
+  </si>
+  <si>
+    <t>OHR</t>
+  </si>
+  <si>
+    <t>2027-04-19</t>
+  </si>
+  <si>
+    <t>2027-04-21</t>
+  </si>
+  <si>
+    <t>2027-04-22</t>
+  </si>
+  <si>
+    <t>2027-04-23</t>
+  </si>
+  <si>
+    <t>Teamfahrt</t>
+  </si>
+  <si>
+    <t>2027-04-26</t>
+  </si>
+  <si>
+    <t>2027-04-28</t>
+  </si>
+  <si>
+    <t>2027-04-29</t>
+  </si>
+  <si>
+    <t>2027-05-12</t>
+  </si>
+  <si>
+    <t>2027-05-13</t>
+  </si>
+  <si>
+    <t>2027-05-19</t>
+  </si>
+  <si>
+    <t>2027-05-20</t>
+  </si>
+  <si>
+    <t>2027-05-26</t>
+  </si>
+  <si>
+    <t>2027-05-27</t>
   </si>
 </sst>
 </file>
@@ -5292,7 +5535,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J108"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="13" style="5" customWidth="1"/>
@@ -5341,22 +5584,22 @@
         <v>278</v>
       </c>
       <c r="B2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D2" t="s">
         <v>279</v>
       </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>280</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -5370,10 +5613,10 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="B3" t="s">
         <v>281</v>
-      </c>
-      <c r="B3" t="s">
-        <v>279</v>
       </c>
       <c r="C3" t="s">
         <v>8</v>
@@ -5405,13 +5648,13 @@
         <v>283</v>
       </c>
       <c r="B4" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -5434,16 +5677,16 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B5" t="s">
         <v>138</v>
       </c>
       <c r="C5" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D5" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -5452,7 +5695,7 @@
         <v>8</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>8</v>
+        <v>287</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -5466,16 +5709,16 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B6" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C6" t="s">
         <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -5498,16 +5741,16 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B7" t="s">
-        <v>138</v>
+        <v>281</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -5530,16 +5773,16 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B8" t="s">
-        <v>279</v>
+        <v>138</v>
       </c>
       <c r="C8" t="s">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>289</v>
+        <v>140</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -5548,7 +5791,7 @@
         <v>8</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>8</v>
+        <v>292</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -5562,16 +5805,16 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B9" t="s">
         <v>138</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>168</v>
       </c>
       <c r="D9" t="s">
-        <v>140</v>
+        <v>279</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -5580,7 +5823,7 @@
         <v>8</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -5594,16 +5837,16 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B10" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -5626,16 +5869,16 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B11" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C11" t="s">
         <v>8</v>
       </c>
       <c r="D11" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -5658,16 +5901,16 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B12" t="s">
         <v>138</v>
       </c>
       <c r="C12" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D12" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -5676,10 +5919,10 @@
         <v>8</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H12" t="s">
-        <v>8</v>
+        <v>296</v>
+      </c>
+      <c r="H12">
+        <v>13</v>
       </c>
       <c r="I12" t="s">
         <v>8</v>
@@ -5690,16 +5933,16 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B13" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C13" t="s">
         <v>8</v>
       </c>
       <c r="D13" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -5722,16 +5965,16 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B14" t="s">
-        <v>138</v>
+        <v>281</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="D14" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -5754,16 +5997,16 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B15" t="s">
-        <v>279</v>
+        <v>138</v>
       </c>
       <c r="C15" t="s">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
-        <v>289</v>
+        <v>140</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -5772,7 +6015,7 @@
         <v>8</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>8</v>
+        <v>299</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -5786,16 +6029,16 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B16" t="s">
-        <v>138</v>
+        <v>281</v>
       </c>
       <c r="C16" t="s">
-        <v>72</v>
+        <v>8</v>
       </c>
       <c r="D16" t="s">
-        <v>140</v>
+        <v>286</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -5804,7 +6047,7 @@
         <v>8</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>297</v>
+        <v>8</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -5818,17 +6061,17 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>296</v>
+        <v>127</v>
       </c>
       <c r="B17" t="s">
+        <v>138</v>
+      </c>
+      <c r="C17" t="s">
+        <v>168</v>
+      </c>
+      <c r="D17" t="s">
         <v>279</v>
       </c>
-      <c r="C17" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" t="s">
-        <v>291</v>
-      </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
@@ -5836,7 +6079,7 @@
         <v>8</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>8</v>
+        <v>300</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -5850,16 +6093,16 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>20</v>
+        <v>127</v>
       </c>
       <c r="B18" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="C18" t="s">
         <v>8</v>
       </c>
       <c r="D18" t="s">
-        <v>8</v>
+        <v>282</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -5868,7 +6111,7 @@
         <v>8</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>299</v>
+        <v>8</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -5882,16 +6125,16 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>300</v>
+        <v>136</v>
       </c>
       <c r="B19" t="s">
-        <v>138</v>
+        <v>281</v>
       </c>
       <c r="C19" t="s">
-        <v>171</v>
+        <v>8</v>
       </c>
       <c r="D19" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -5917,13 +6160,13 @@
         <v>301</v>
       </c>
       <c r="B20" t="s">
-        <v>279</v>
+        <v>138</v>
       </c>
       <c r="C20" t="s">
-        <v>8</v>
+        <v>166</v>
       </c>
       <c r="D20" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -5932,10 +6175,10 @@
         <v>8</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H20" t="s">
-        <v>8</v>
+        <v>302</v>
+      </c>
+      <c r="H20">
+        <v>12</v>
       </c>
       <c r="I20" t="s">
         <v>8</v>
@@ -5946,13 +6189,13 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B21" t="s">
-        <v>138</v>
+        <v>281</v>
       </c>
       <c r="C21" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="D21" t="s">
         <v>288</v>
@@ -5978,16 +6221,16 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B22" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C22" t="s">
         <v>8</v>
       </c>
       <c r="D22" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -6010,7 +6253,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B23" t="s">
         <v>138</v>
@@ -6028,15 +6271,2735 @@
         <v>8</v>
       </c>
       <c r="G23" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="H23" t="s">
+        <v>8</v>
+      </c>
+      <c r="I23" t="s">
+        <v>8</v>
+      </c>
+      <c r="J23" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="H23" t="s">
-        <v>8</v>
-      </c>
-      <c r="I23" t="s">
-        <v>8</v>
-      </c>
-      <c r="J23" t="s">
+      <c r="B24" t="s">
+        <v>281</v>
+      </c>
+      <c r="C24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" t="s">
+        <v>286</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" t="s">
+        <v>8</v>
+      </c>
+      <c r="J24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="B25" t="s">
+        <v>281</v>
+      </c>
+      <c r="C25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" t="s">
+        <v>279</v>
+      </c>
+      <c r="E25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" t="s">
+        <v>8</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H25" t="s">
+        <v>8</v>
+      </c>
+      <c r="I25" t="s">
+        <v>8</v>
+      </c>
+      <c r="J25" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="B26" t="s">
+        <v>281</v>
+      </c>
+      <c r="C26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" t="s">
+        <v>286</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H26" t="s">
+        <v>8</v>
+      </c>
+      <c r="I26" t="s">
+        <v>8</v>
+      </c>
+      <c r="J26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="B27" t="s">
+        <v>281</v>
+      </c>
+      <c r="C27" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" t="s">
+        <v>279</v>
+      </c>
+      <c r="E27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H27" t="s">
+        <v>8</v>
+      </c>
+      <c r="I27" t="s">
+        <v>8</v>
+      </c>
+      <c r="J27" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="B28" t="s">
+        <v>138</v>
+      </c>
+      <c r="C28" t="s">
+        <v>171</v>
+      </c>
+      <c r="D28" t="s">
+        <v>310</v>
+      </c>
+      <c r="E28" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" t="s">
+        <v>8</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H28" t="s">
+        <v>8</v>
+      </c>
+      <c r="I28" t="s">
+        <v>8</v>
+      </c>
+      <c r="J28" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="B29" t="s">
+        <v>281</v>
+      </c>
+      <c r="C29" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" t="s">
+        <v>286</v>
+      </c>
+      <c r="E29" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" t="s">
+        <v>8</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H29" t="s">
+        <v>8</v>
+      </c>
+      <c r="I29" t="s">
+        <v>8</v>
+      </c>
+      <c r="J29" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="B30" t="s">
+        <v>138</v>
+      </c>
+      <c r="C30" t="s">
+        <v>44</v>
+      </c>
+      <c r="D30" t="s">
+        <v>284</v>
+      </c>
+      <c r="E30" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" t="s">
+        <v>8</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H30" t="s">
+        <v>8</v>
+      </c>
+      <c r="I30" t="s">
+        <v>8</v>
+      </c>
+      <c r="J30" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="B31" t="s">
+        <v>281</v>
+      </c>
+      <c r="C31" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" t="s">
+        <v>290</v>
+      </c>
+      <c r="E31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31" t="s">
+        <v>8</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H31" t="s">
+        <v>8</v>
+      </c>
+      <c r="I31" t="s">
+        <v>8</v>
+      </c>
+      <c r="J31" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B32" t="s">
+        <v>138</v>
+      </c>
+      <c r="C32" t="s">
+        <v>72</v>
+      </c>
+      <c r="D32" t="s">
+        <v>140</v>
+      </c>
+      <c r="E32" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="H32" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B33" t="s">
+        <v>281</v>
+      </c>
+      <c r="C33" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" t="s">
+        <v>288</v>
+      </c>
+      <c r="E33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" t="s">
+        <v>8</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H33" t="s">
+        <v>8</v>
+      </c>
+      <c r="I33" t="s">
+        <v>8</v>
+      </c>
+      <c r="J33" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="B34" t="s">
+        <v>281</v>
+      </c>
+      <c r="C34" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" t="s">
+        <v>279</v>
+      </c>
+      <c r="E34" t="s">
+        <v>8</v>
+      </c>
+      <c r="F34" t="s">
+        <v>8</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H34" t="s">
+        <v>8</v>
+      </c>
+      <c r="I34" t="s">
+        <v>8</v>
+      </c>
+      <c r="J34" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="B35" t="s">
+        <v>138</v>
+      </c>
+      <c r="C35" t="s">
+        <v>171</v>
+      </c>
+      <c r="D35" t="s">
+        <v>310</v>
+      </c>
+      <c r="E35" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" t="s">
+        <v>8</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H35" t="s">
+        <v>8</v>
+      </c>
+      <c r="I35" t="s">
+        <v>8</v>
+      </c>
+      <c r="J35" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="B36" t="s">
+        <v>281</v>
+      </c>
+      <c r="C36" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" t="s">
+        <v>279</v>
+      </c>
+      <c r="E36" t="s">
+        <v>8</v>
+      </c>
+      <c r="F36" t="s">
+        <v>8</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H36" t="s">
+        <v>8</v>
+      </c>
+      <c r="I36" t="s">
+        <v>8</v>
+      </c>
+      <c r="J36" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="B37" t="s">
+        <v>138</v>
+      </c>
+      <c r="C37" t="s">
+        <v>44</v>
+      </c>
+      <c r="D37" t="s">
+        <v>284</v>
+      </c>
+      <c r="E37" t="s">
+        <v>8</v>
+      </c>
+      <c r="F37" t="s">
+        <v>8</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H37" t="s">
+        <v>8</v>
+      </c>
+      <c r="I37" t="s">
+        <v>8</v>
+      </c>
+      <c r="J37" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="B38" t="s">
+        <v>281</v>
+      </c>
+      <c r="C38" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" t="s">
+        <v>290</v>
+      </c>
+      <c r="E38" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" t="s">
+        <v>8</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H38" t="s">
+        <v>8</v>
+      </c>
+      <c r="I38" t="s">
+        <v>8</v>
+      </c>
+      <c r="J38" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="B39" t="s">
+        <v>138</v>
+      </c>
+      <c r="C39" t="s">
+        <v>72</v>
+      </c>
+      <c r="D39" t="s">
+        <v>140</v>
+      </c>
+      <c r="E39" t="s">
+        <v>8</v>
+      </c>
+      <c r="F39" t="s">
+        <v>8</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="H39" t="s">
+        <v>8</v>
+      </c>
+      <c r="I39" t="s">
+        <v>8</v>
+      </c>
+      <c r="J39" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="B40" t="s">
+        <v>281</v>
+      </c>
+      <c r="C40" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" t="s">
+        <v>288</v>
+      </c>
+      <c r="E40" t="s">
+        <v>8</v>
+      </c>
+      <c r="F40" t="s">
+        <v>8</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H40" t="s">
+        <v>8</v>
+      </c>
+      <c r="I40" t="s">
+        <v>8</v>
+      </c>
+      <c r="J40" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B41" t="s">
+        <v>320</v>
+      </c>
+      <c r="C41" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" t="s">
+        <v>8</v>
+      </c>
+      <c r="F41" t="s">
+        <v>8</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="H41" t="s">
+        <v>8</v>
+      </c>
+      <c r="I41" t="s">
+        <v>8</v>
+      </c>
+      <c r="J41" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="B42" t="s">
+        <v>138</v>
+      </c>
+      <c r="C42" t="s">
+        <v>171</v>
+      </c>
+      <c r="D42" t="s">
+        <v>310</v>
+      </c>
+      <c r="E42" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42" t="s">
+        <v>8</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H42" t="s">
+        <v>8</v>
+      </c>
+      <c r="I42" t="s">
+        <v>8</v>
+      </c>
+      <c r="J42" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="B43" t="s">
+        <v>281</v>
+      </c>
+      <c r="C43" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" t="s">
+        <v>279</v>
+      </c>
+      <c r="E43" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" t="s">
+        <v>8</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H43" t="s">
+        <v>8</v>
+      </c>
+      <c r="I43" t="s">
+        <v>8</v>
+      </c>
+      <c r="J43" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="B44" t="s">
+        <v>138</v>
+      </c>
+      <c r="C44" t="s">
+        <v>44</v>
+      </c>
+      <c r="D44" t="s">
+        <v>284</v>
+      </c>
+      <c r="E44" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="B45" t="s">
+        <v>281</v>
+      </c>
+      <c r="C45" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" t="s">
+        <v>290</v>
+      </c>
+      <c r="E45" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="B46" t="s">
+        <v>138</v>
+      </c>
+      <c r="C46" t="s">
+        <v>72</v>
+      </c>
+      <c r="D46" t="s">
+        <v>140</v>
+      </c>
+      <c r="E46" t="s">
+        <v>8</v>
+      </c>
+      <c r="F46" t="s">
+        <v>8</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="H46" t="s">
+        <v>8</v>
+      </c>
+      <c r="I46" t="s">
+        <v>8</v>
+      </c>
+      <c r="J46" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="B47" t="s">
+        <v>281</v>
+      </c>
+      <c r="C47" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" t="s">
+        <v>288</v>
+      </c>
+      <c r="E47" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="B48" t="s">
+        <v>281</v>
+      </c>
+      <c r="C48" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" t="s">
+        <v>279</v>
+      </c>
+      <c r="E48" t="s">
+        <v>8</v>
+      </c>
+      <c r="F48" t="s">
+        <v>8</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H48" t="s">
+        <v>8</v>
+      </c>
+      <c r="I48" t="s">
+        <v>8</v>
+      </c>
+      <c r="J48" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="B49" t="s">
+        <v>281</v>
+      </c>
+      <c r="C49" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" t="s">
+        <v>282</v>
+      </c>
+      <c r="E49" t="s">
+        <v>8</v>
+      </c>
+      <c r="F49" t="s">
+        <v>8</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H49" t="s">
+        <v>8</v>
+      </c>
+      <c r="I49" t="s">
+        <v>8</v>
+      </c>
+      <c r="J49" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="B50" t="s">
+        <v>138</v>
+      </c>
+      <c r="C50" t="s">
+        <v>168</v>
+      </c>
+      <c r="D50" t="s">
+        <v>279</v>
+      </c>
+      <c r="E50" t="s">
+        <v>8</v>
+      </c>
+      <c r="F50" t="s">
+        <v>8</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H50" t="s">
+        <v>8</v>
+      </c>
+      <c r="I50" t="s">
+        <v>8</v>
+      </c>
+      <c r="J50" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="B51" t="s">
+        <v>281</v>
+      </c>
+      <c r="C51" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" t="s">
+        <v>286</v>
+      </c>
+      <c r="E51" t="s">
+        <v>8</v>
+      </c>
+      <c r="F51" t="s">
+        <v>8</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H51" t="s">
+        <v>8</v>
+      </c>
+      <c r="I51" t="s">
+        <v>8</v>
+      </c>
+      <c r="J51" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="B52" t="s">
+        <v>138</v>
+      </c>
+      <c r="C52" t="s">
+        <v>166</v>
+      </c>
+      <c r="D52" t="s">
+        <v>290</v>
+      </c>
+      <c r="E52" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" t="s">
+        <v>8</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H52" t="s">
+        <v>8</v>
+      </c>
+      <c r="I52" t="s">
+        <v>8</v>
+      </c>
+      <c r="J52" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="B53" t="s">
+        <v>281</v>
+      </c>
+      <c r="C53" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E53" t="s">
+        <v>8</v>
+      </c>
+      <c r="F53" t="s">
+        <v>8</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H53" t="s">
+        <v>8</v>
+      </c>
+      <c r="I53" t="s">
+        <v>8</v>
+      </c>
+      <c r="J53" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="B54" t="s">
+        <v>281</v>
+      </c>
+      <c r="C54" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54" t="s">
+        <v>286</v>
+      </c>
+      <c r="E54" t="s">
+        <v>8</v>
+      </c>
+      <c r="F54" t="s">
+        <v>8</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H54" t="s">
+        <v>8</v>
+      </c>
+      <c r="I54" t="s">
+        <v>8</v>
+      </c>
+      <c r="J54" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="B55" t="s">
+        <v>281</v>
+      </c>
+      <c r="C55" t="s">
+        <v>8</v>
+      </c>
+      <c r="D55" t="s">
+        <v>282</v>
+      </c>
+      <c r="E55" t="s">
+        <v>8</v>
+      </c>
+      <c r="F55" t="s">
+        <v>8</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H55" t="s">
+        <v>8</v>
+      </c>
+      <c r="I55" t="s">
+        <v>8</v>
+      </c>
+      <c r="J55" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="B56" t="s">
+        <v>138</v>
+      </c>
+      <c r="C56" t="s">
+        <v>72</v>
+      </c>
+      <c r="D56" t="s">
+        <v>140</v>
+      </c>
+      <c r="E56" t="s">
+        <v>8</v>
+      </c>
+      <c r="F56" t="s">
+        <v>8</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H56" t="s">
+        <v>8</v>
+      </c>
+      <c r="I56" t="s">
+        <v>8</v>
+      </c>
+      <c r="J56" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="B57" t="s">
+        <v>138</v>
+      </c>
+      <c r="C57" t="s">
+        <v>168</v>
+      </c>
+      <c r="D57" t="s">
+        <v>279</v>
+      </c>
+      <c r="E57" t="s">
+        <v>8</v>
+      </c>
+      <c r="F57" t="s">
+        <v>8</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H57" t="s">
+        <v>8</v>
+      </c>
+      <c r="I57" t="s">
+        <v>8</v>
+      </c>
+      <c r="J57" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="B58" t="s">
+        <v>138</v>
+      </c>
+      <c r="C58" t="s">
+        <v>166</v>
+      </c>
+      <c r="D58" t="s">
+        <v>290</v>
+      </c>
+      <c r="E58" t="s">
+        <v>8</v>
+      </c>
+      <c r="F58" t="s">
+        <v>8</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H58" t="s">
+        <v>8</v>
+      </c>
+      <c r="I58" t="s">
+        <v>8</v>
+      </c>
+      <c r="J58" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="B59" t="s">
+        <v>281</v>
+      </c>
+      <c r="C59" t="s">
+        <v>8</v>
+      </c>
+      <c r="D59" t="s">
+        <v>284</v>
+      </c>
+      <c r="E59" t="s">
+        <v>8</v>
+      </c>
+      <c r="F59" t="s">
+        <v>8</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H59" t="s">
+        <v>8</v>
+      </c>
+      <c r="I59" t="s">
+        <v>8</v>
+      </c>
+      <c r="J59" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="B60" t="s">
+        <v>281</v>
+      </c>
+      <c r="C60" t="s">
+        <v>8</v>
+      </c>
+      <c r="D60" t="s">
+        <v>282</v>
+      </c>
+      <c r="E60" t="s">
+        <v>8</v>
+      </c>
+      <c r="F60" t="s">
+        <v>8</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H60" t="s">
+        <v>8</v>
+      </c>
+      <c r="I60" t="s">
+        <v>8</v>
+      </c>
+      <c r="J60" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="B61" t="s">
+        <v>138</v>
+      </c>
+      <c r="C61" t="s">
+        <v>72</v>
+      </c>
+      <c r="D61" t="s">
+        <v>140</v>
+      </c>
+      <c r="E61" t="s">
+        <v>8</v>
+      </c>
+      <c r="F61" t="s">
+        <v>8</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H61" t="s">
+        <v>8</v>
+      </c>
+      <c r="I61" t="s">
+        <v>8</v>
+      </c>
+      <c r="J61" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="B62" t="s">
+        <v>138</v>
+      </c>
+      <c r="C62" t="s">
+        <v>168</v>
+      </c>
+      <c r="D62" t="s">
+        <v>279</v>
+      </c>
+      <c r="E62" t="s">
+        <v>8</v>
+      </c>
+      <c r="F62" t="s">
+        <v>8</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H62" t="s">
+        <v>8</v>
+      </c>
+      <c r="I62" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="B63" t="s">
+        <v>281</v>
+      </c>
+      <c r="C63" t="s">
+        <v>8</v>
+      </c>
+      <c r="D63" t="s">
+        <v>286</v>
+      </c>
+      <c r="E63" t="s">
+        <v>8</v>
+      </c>
+      <c r="F63" t="s">
+        <v>8</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H63" t="s">
+        <v>8</v>
+      </c>
+      <c r="I63" t="s">
+        <v>8</v>
+      </c>
+      <c r="J63" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="B64" t="s">
+        <v>138</v>
+      </c>
+      <c r="C64" t="s">
+        <v>166</v>
+      </c>
+      <c r="D64" t="s">
+        <v>290</v>
+      </c>
+      <c r="E64" t="s">
+        <v>8</v>
+      </c>
+      <c r="F64" t="s">
+        <v>8</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H64" t="s">
+        <v>8</v>
+      </c>
+      <c r="I64" t="s">
+        <v>8</v>
+      </c>
+      <c r="J64" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A65" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="B65" t="s">
+        <v>281</v>
+      </c>
+      <c r="C65" t="s">
+        <v>8</v>
+      </c>
+      <c r="D65" t="s">
+        <v>284</v>
+      </c>
+      <c r="E65" t="s">
+        <v>8</v>
+      </c>
+      <c r="F65" t="s">
+        <v>8</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H65" t="s">
+        <v>8</v>
+      </c>
+      <c r="I65" t="s">
+        <v>8</v>
+      </c>
+      <c r="J65" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="B66" t="s">
+        <v>138</v>
+      </c>
+      <c r="C66" t="s">
+        <v>72</v>
+      </c>
+      <c r="D66" t="s">
+        <v>140</v>
+      </c>
+      <c r="E66" t="s">
+        <v>8</v>
+      </c>
+      <c r="F66" t="s">
+        <v>8</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H66" t="s">
+        <v>8</v>
+      </c>
+      <c r="I66" t="s">
+        <v>8</v>
+      </c>
+      <c r="J66" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="B67" t="s">
+        <v>138</v>
+      </c>
+      <c r="C67" t="s">
+        <v>171</v>
+      </c>
+      <c r="D67" t="s">
+        <v>310</v>
+      </c>
+      <c r="E67" t="s">
+        <v>8</v>
+      </c>
+      <c r="F67" t="s">
+        <v>8</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H67" t="s">
+        <v>8</v>
+      </c>
+      <c r="I67" t="s">
+        <v>8</v>
+      </c>
+      <c r="J67" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="B68" t="s">
+        <v>138</v>
+      </c>
+      <c r="C68" t="s">
+        <v>168</v>
+      </c>
+      <c r="D68" t="s">
+        <v>279</v>
+      </c>
+      <c r="E68" t="s">
+        <v>8</v>
+      </c>
+      <c r="F68" t="s">
+        <v>8</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H68" t="s">
+        <v>8</v>
+      </c>
+      <c r="I68" t="s">
+        <v>8</v>
+      </c>
+      <c r="J68" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="B69" t="s">
+        <v>138</v>
+      </c>
+      <c r="C69" t="s">
+        <v>44</v>
+      </c>
+      <c r="D69" t="s">
+        <v>282</v>
+      </c>
+      <c r="E69" t="s">
+        <v>8</v>
+      </c>
+      <c r="F69" t="s">
+        <v>8</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H69" t="s">
+        <v>8</v>
+      </c>
+      <c r="I69" t="s">
+        <v>8</v>
+      </c>
+      <c r="J69" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="B70" t="s">
+        <v>138</v>
+      </c>
+      <c r="C70" t="s">
+        <v>171</v>
+      </c>
+      <c r="D70" t="s">
+        <v>310</v>
+      </c>
+      <c r="E70" t="s">
+        <v>8</v>
+      </c>
+      <c r="F70" t="s">
+        <v>8</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H70" t="s">
+        <v>8</v>
+      </c>
+      <c r="I70" t="s">
+        <v>8</v>
+      </c>
+      <c r="J70" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A71" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="B71" t="s">
+        <v>138</v>
+      </c>
+      <c r="C71" t="s">
+        <v>168</v>
+      </c>
+      <c r="D71" t="s">
+        <v>279</v>
+      </c>
+      <c r="E71" t="s">
+        <v>8</v>
+      </c>
+      <c r="F71" t="s">
+        <v>8</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H71" t="s">
+        <v>8</v>
+      </c>
+      <c r="I71" t="s">
+        <v>8</v>
+      </c>
+      <c r="J71" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="B72" t="s">
+        <v>138</v>
+      </c>
+      <c r="C72" t="s">
+        <v>44</v>
+      </c>
+      <c r="D72" t="s">
+        <v>282</v>
+      </c>
+      <c r="E72" t="s">
+        <v>8</v>
+      </c>
+      <c r="F72" t="s">
+        <v>8</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H72" t="s">
+        <v>8</v>
+      </c>
+      <c r="I72" t="s">
+        <v>8</v>
+      </c>
+      <c r="J72" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A73" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="B73" t="s">
+        <v>138</v>
+      </c>
+      <c r="C73" t="s">
+        <v>171</v>
+      </c>
+      <c r="D73" t="s">
+        <v>310</v>
+      </c>
+      <c r="E73" t="s">
+        <v>8</v>
+      </c>
+      <c r="F73" t="s">
+        <v>8</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H73" t="s">
+        <v>8</v>
+      </c>
+      <c r="I73" t="s">
+        <v>8</v>
+      </c>
+      <c r="J73" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A74" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="B74" t="s">
+        <v>138</v>
+      </c>
+      <c r="C74" t="s">
+        <v>168</v>
+      </c>
+      <c r="D74" t="s">
+        <v>279</v>
+      </c>
+      <c r="E74" t="s">
+        <v>8</v>
+      </c>
+      <c r="F74" t="s">
+        <v>8</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H74" t="s">
+        <v>8</v>
+      </c>
+      <c r="I74" t="s">
+        <v>8</v>
+      </c>
+      <c r="J74" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A75" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="B75" t="s">
+        <v>138</v>
+      </c>
+      <c r="C75" t="s">
+        <v>44</v>
+      </c>
+      <c r="D75" t="s">
+        <v>282</v>
+      </c>
+      <c r="E75" t="s">
+        <v>8</v>
+      </c>
+      <c r="F75" t="s">
+        <v>8</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H75" t="s">
+        <v>8</v>
+      </c>
+      <c r="I75" t="s">
+        <v>8</v>
+      </c>
+      <c r="J75" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="B76" t="s">
+        <v>138</v>
+      </c>
+      <c r="C76" t="s">
+        <v>166</v>
+      </c>
+      <c r="D76" t="s">
+        <v>288</v>
+      </c>
+      <c r="E76" t="s">
+        <v>8</v>
+      </c>
+      <c r="F76" t="s">
+        <v>8</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H76" t="s">
+        <v>8</v>
+      </c>
+      <c r="I76" t="s">
+        <v>8</v>
+      </c>
+      <c r="J76" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="B77" t="s">
+        <v>138</v>
+      </c>
+      <c r="C77" t="s">
+        <v>171</v>
+      </c>
+      <c r="D77" t="s">
+        <v>310</v>
+      </c>
+      <c r="E77" t="s">
+        <v>8</v>
+      </c>
+      <c r="F77" t="s">
+        <v>8</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H77" t="s">
+        <v>8</v>
+      </c>
+      <c r="I77" t="s">
+        <v>8</v>
+      </c>
+      <c r="J77" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="B78" t="s">
+        <v>138</v>
+      </c>
+      <c r="C78" t="s">
+        <v>72</v>
+      </c>
+      <c r="D78" t="s">
+        <v>353</v>
+      </c>
+      <c r="E78" t="s">
+        <v>8</v>
+      </c>
+      <c r="F78" t="s">
+        <v>8</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H78" t="s">
+        <v>8</v>
+      </c>
+      <c r="I78" t="s">
+        <v>8</v>
+      </c>
+      <c r="J78" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A79" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="B79" t="s">
+        <v>138</v>
+      </c>
+      <c r="C79" t="s">
+        <v>171</v>
+      </c>
+      <c r="D79" t="s">
+        <v>310</v>
+      </c>
+      <c r="E79" t="s">
+        <v>8</v>
+      </c>
+      <c r="F79" t="s">
+        <v>8</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H79" t="s">
+        <v>8</v>
+      </c>
+      <c r="I79" t="s">
+        <v>8</v>
+      </c>
+      <c r="J79" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="B80" t="s">
+        <v>138</v>
+      </c>
+      <c r="C80" t="s">
+        <v>166</v>
+      </c>
+      <c r="D80" t="s">
+        <v>290</v>
+      </c>
+      <c r="E80" t="s">
+        <v>8</v>
+      </c>
+      <c r="F80" t="s">
+        <v>8</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H80" t="s">
+        <v>8</v>
+      </c>
+      <c r="I80" t="s">
+        <v>8</v>
+      </c>
+      <c r="J80" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A81" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="B81" t="s">
+        <v>138</v>
+      </c>
+      <c r="C81" t="s">
+        <v>72</v>
+      </c>
+      <c r="D81" t="s">
+        <v>353</v>
+      </c>
+      <c r="E81" t="s">
+        <v>8</v>
+      </c>
+      <c r="F81" t="s">
+        <v>8</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H81" t="s">
+        <v>8</v>
+      </c>
+      <c r="I81" t="s">
+        <v>8</v>
+      </c>
+      <c r="J81" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A82" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="B82" t="s">
+        <v>320</v>
+      </c>
+      <c r="C82" t="s">
+        <v>8</v>
+      </c>
+      <c r="D82" t="s">
+        <v>8</v>
+      </c>
+      <c r="E82" t="s">
+        <v>8</v>
+      </c>
+      <c r="F82" t="s">
+        <v>8</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="H82" t="s">
+        <v>8</v>
+      </c>
+      <c r="I82" t="s">
+        <v>8</v>
+      </c>
+      <c r="J82" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A83" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="B83" t="s">
+        <v>138</v>
+      </c>
+      <c r="C83" t="s">
+        <v>166</v>
+      </c>
+      <c r="D83" t="s">
+        <v>288</v>
+      </c>
+      <c r="E83" t="s">
+        <v>8</v>
+      </c>
+      <c r="F83" t="s">
+        <v>8</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H83" t="s">
+        <v>8</v>
+      </c>
+      <c r="I83" t="s">
+        <v>8</v>
+      </c>
+      <c r="J83" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A84" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="B84" t="s">
+        <v>138</v>
+      </c>
+      <c r="C84" t="s">
+        <v>171</v>
+      </c>
+      <c r="D84" t="s">
+        <v>310</v>
+      </c>
+      <c r="E84" t="s">
+        <v>8</v>
+      </c>
+      <c r="F84" t="s">
+        <v>8</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H84" t="s">
+        <v>8</v>
+      </c>
+      <c r="I84" t="s">
+        <v>8</v>
+      </c>
+      <c r="J84" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A85" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="B85" t="s">
+        <v>138</v>
+      </c>
+      <c r="C85" t="s">
+        <v>72</v>
+      </c>
+      <c r="D85" t="s">
+        <v>353</v>
+      </c>
+      <c r="E85" t="s">
+        <v>8</v>
+      </c>
+      <c r="F85" t="s">
+        <v>8</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H85" t="s">
+        <v>8</v>
+      </c>
+      <c r="I85" t="s">
+        <v>8</v>
+      </c>
+      <c r="J85" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A86" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="B86" t="s">
+        <v>138</v>
+      </c>
+      <c r="C86" t="s">
+        <v>166</v>
+      </c>
+      <c r="D86" t="s">
+        <v>290</v>
+      </c>
+      <c r="E86" t="s">
+        <v>8</v>
+      </c>
+      <c r="F86" t="s">
+        <v>8</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H86" t="s">
+        <v>8</v>
+      </c>
+      <c r="I86" t="s">
+        <v>8</v>
+      </c>
+      <c r="J86" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A87" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="B87" t="s">
+        <v>138</v>
+      </c>
+      <c r="C87" t="s">
+        <v>44</v>
+      </c>
+      <c r="D87" t="s">
+        <v>284</v>
+      </c>
+      <c r="E87" t="s">
+        <v>8</v>
+      </c>
+      <c r="F87" t="s">
+        <v>8</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H87" t="s">
+        <v>8</v>
+      </c>
+      <c r="I87" t="s">
+        <v>8</v>
+      </c>
+      <c r="J87" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A88" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="B88" t="s">
+        <v>138</v>
+      </c>
+      <c r="C88" t="s">
+        <v>166</v>
+      </c>
+      <c r="D88" t="s">
+        <v>290</v>
+      </c>
+      <c r="E88" t="s">
+        <v>8</v>
+      </c>
+      <c r="F88" t="s">
+        <v>8</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H88" t="s">
+        <v>8</v>
+      </c>
+      <c r="I88" t="s">
+        <v>8</v>
+      </c>
+      <c r="J88" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A89" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="B89" t="s">
+        <v>138</v>
+      </c>
+      <c r="C89" t="s">
+        <v>44</v>
+      </c>
+      <c r="D89" t="s">
+        <v>284</v>
+      </c>
+      <c r="E89" t="s">
+        <v>8</v>
+      </c>
+      <c r="F89" t="s">
+        <v>8</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H89" t="s">
+        <v>8</v>
+      </c>
+      <c r="I89" t="s">
+        <v>8</v>
+      </c>
+      <c r="J89" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A90" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="B90" t="s">
+        <v>138</v>
+      </c>
+      <c r="C90" t="s">
+        <v>166</v>
+      </c>
+      <c r="D90" t="s">
+        <v>290</v>
+      </c>
+      <c r="E90" t="s">
+        <v>8</v>
+      </c>
+      <c r="F90" t="s">
+        <v>8</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H90" t="s">
+        <v>8</v>
+      </c>
+      <c r="I90" t="s">
+        <v>8</v>
+      </c>
+      <c r="J90" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A91" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="B91" t="s">
+        <v>138</v>
+      </c>
+      <c r="C91" t="s">
+        <v>44</v>
+      </c>
+      <c r="D91" t="s">
+        <v>284</v>
+      </c>
+      <c r="E91" t="s">
+        <v>8</v>
+      </c>
+      <c r="F91" t="s">
+        <v>8</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H91" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" t="s">
+        <v>8</v>
+      </c>
+      <c r="J91" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A92" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="B92" t="s">
+        <v>138</v>
+      </c>
+      <c r="C92" t="s">
+        <v>44</v>
+      </c>
+      <c r="D92" t="s">
+        <v>282</v>
+      </c>
+      <c r="E92" t="s">
+        <v>8</v>
+      </c>
+      <c r="F92" t="s">
+        <v>8</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H92" t="s">
+        <v>8</v>
+      </c>
+      <c r="I92" t="s">
+        <v>8</v>
+      </c>
+      <c r="J92" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A93" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="B93" t="s">
+        <v>138</v>
+      </c>
+      <c r="C93" t="s">
+        <v>166</v>
+      </c>
+      <c r="D93" t="s">
+        <v>288</v>
+      </c>
+      <c r="E93" t="s">
+        <v>8</v>
+      </c>
+      <c r="F93" t="s">
+        <v>8</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H93" t="s">
+        <v>8</v>
+      </c>
+      <c r="I93" t="s">
+        <v>8</v>
+      </c>
+      <c r="J93" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A94" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="B94" t="s">
+        <v>320</v>
+      </c>
+      <c r="C94" t="s">
+        <v>8</v>
+      </c>
+      <c r="D94" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" t="s">
+        <v>8</v>
+      </c>
+      <c r="F94" t="s">
+        <v>8</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="H94" t="s">
+        <v>8</v>
+      </c>
+      <c r="I94" t="s">
+        <v>8</v>
+      </c>
+      <c r="J94" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A95" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="B95" t="s">
+        <v>138</v>
+      </c>
+      <c r="C95" t="s">
+        <v>72</v>
+      </c>
+      <c r="D95" t="s">
+        <v>371</v>
+      </c>
+      <c r="E95" t="s">
+        <v>8</v>
+      </c>
+      <c r="F95" t="s">
+        <v>8</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H95" t="s">
+        <v>8</v>
+      </c>
+      <c r="I95" t="s">
+        <v>8</v>
+      </c>
+      <c r="J95" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A96" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="B96" t="s">
+        <v>138</v>
+      </c>
+      <c r="C96" t="s">
+        <v>44</v>
+      </c>
+      <c r="D96" t="s">
+        <v>282</v>
+      </c>
+      <c r="E96" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A97" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="B97" t="s">
+        <v>138</v>
+      </c>
+      <c r="C97" t="s">
+        <v>166</v>
+      </c>
+      <c r="D97" t="s">
+        <v>288</v>
+      </c>
+      <c r="E97" t="s">
+        <v>8</v>
+      </c>
+      <c r="F97" t="s">
+        <v>8</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H97" t="s">
+        <v>8</v>
+      </c>
+      <c r="I97" t="s">
+        <v>8</v>
+      </c>
+      <c r="J97" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A98" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="B98" t="s">
+        <v>138</v>
+      </c>
+      <c r="C98" t="s">
+        <v>72</v>
+      </c>
+      <c r="D98" t="s">
+        <v>371</v>
+      </c>
+      <c r="E98" t="s">
+        <v>8</v>
+      </c>
+      <c r="F98" t="s">
+        <v>8</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H98" t="s">
+        <v>8</v>
+      </c>
+      <c r="I98" t="s">
+        <v>8</v>
+      </c>
+      <c r="J98" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A99" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="B99" t="s">
+        <v>320</v>
+      </c>
+      <c r="C99" t="s">
+        <v>8</v>
+      </c>
+      <c r="D99" t="s">
+        <v>8</v>
+      </c>
+      <c r="E99" t="s">
+        <v>8</v>
+      </c>
+      <c r="F99" t="s">
+        <v>8</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="H99" t="s">
+        <v>8</v>
+      </c>
+      <c r="I99" t="s">
+        <v>8</v>
+      </c>
+      <c r="J99" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A100" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="B100" t="s">
+        <v>138</v>
+      </c>
+      <c r="C100" t="s">
+        <v>44</v>
+      </c>
+      <c r="D100" t="s">
+        <v>282</v>
+      </c>
+      <c r="E100" t="s">
+        <v>8</v>
+      </c>
+      <c r="F100" t="s">
+        <v>8</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H100" t="s">
+        <v>8</v>
+      </c>
+      <c r="I100" t="s">
+        <v>8</v>
+      </c>
+      <c r="J100" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A101" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="B101" t="s">
+        <v>138</v>
+      </c>
+      <c r="C101" t="s">
+        <v>166</v>
+      </c>
+      <c r="D101" t="s">
+        <v>288</v>
+      </c>
+      <c r="E101" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A102" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="B102" t="s">
+        <v>138</v>
+      </c>
+      <c r="C102" t="s">
+        <v>72</v>
+      </c>
+      <c r="D102" t="s">
+        <v>371</v>
+      </c>
+      <c r="E102" t="s">
+        <v>8</v>
+      </c>
+      <c r="F102" t="s">
+        <v>8</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H102" t="s">
+        <v>8</v>
+      </c>
+      <c r="I102" t="s">
+        <v>8</v>
+      </c>
+      <c r="J102" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A103" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="B103" t="s">
+        <v>138</v>
+      </c>
+      <c r="C103" t="s">
+        <v>171</v>
+      </c>
+      <c r="D103" t="s">
+        <v>310</v>
+      </c>
+      <c r="E103" t="s">
+        <v>8</v>
+      </c>
+      <c r="F103" t="s">
+        <v>8</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H103" t="s">
+        <v>8</v>
+      </c>
+      <c r="I103" t="s">
+        <v>8</v>
+      </c>
+      <c r="J103" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A104" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="B104" t="s">
+        <v>138</v>
+      </c>
+      <c r="C104" t="s">
+        <v>44</v>
+      </c>
+      <c r="D104" t="s">
+        <v>284</v>
+      </c>
+      <c r="E104" t="s">
+        <v>8</v>
+      </c>
+      <c r="F104" t="s">
+        <v>8</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H104" t="s">
+        <v>8</v>
+      </c>
+      <c r="I104" t="s">
+        <v>8</v>
+      </c>
+      <c r="J104" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A105" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="B105" t="s">
+        <v>138</v>
+      </c>
+      <c r="C105" t="s">
+        <v>171</v>
+      </c>
+      <c r="D105" t="s">
+        <v>310</v>
+      </c>
+      <c r="E105" t="s">
+        <v>8</v>
+      </c>
+      <c r="F105" t="s">
+        <v>8</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H105" t="s">
+        <v>8</v>
+      </c>
+      <c r="I105" t="s">
+        <v>8</v>
+      </c>
+      <c r="J105" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A106" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="B106" t="s">
+        <v>138</v>
+      </c>
+      <c r="C106" t="s">
+        <v>44</v>
+      </c>
+      <c r="D106" t="s">
+        <v>284</v>
+      </c>
+      <c r="E106" t="s">
+        <v>8</v>
+      </c>
+      <c r="F106" t="s">
+        <v>8</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H106" t="s">
+        <v>8</v>
+      </c>
+      <c r="I106" t="s">
+        <v>8</v>
+      </c>
+      <c r="J106" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A107" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="B107" t="s">
+        <v>138</v>
+      </c>
+      <c r="C107" t="s">
+        <v>171</v>
+      </c>
+      <c r="D107" t="s">
+        <v>310</v>
+      </c>
+      <c r="E107" t="s">
+        <v>8</v>
+      </c>
+      <c r="F107" t="s">
+        <v>8</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H107" t="s">
+        <v>8</v>
+      </c>
+      <c r="I107" t="s">
+        <v>8</v>
+      </c>
+      <c r="J107" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A108" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="B108" t="s">
+        <v>138</v>
+      </c>
+      <c r="C108" t="s">
+        <v>44</v>
+      </c>
+      <c r="D108" t="s">
+        <v>284</v>
+      </c>
+      <c r="E108" t="s">
+        <v>8</v>
+      </c>
+      <c r="F108" t="s">
+        <v>8</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H108" t="s">
+        <v>8</v>
+      </c>
+      <c r="I108" t="s">
+        <v>8</v>
+      </c>
+      <c r="J108" t="s">
         <v>8</v>
       </c>
     </row>

--- a/content/jahrgaenge/Jg7.xlsx
+++ b/content/jahrgaenge/Jg7.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1964" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1974" uniqueCount="388">
   <si>
     <t>Hinweise zu Jg7.xlsx</t>
   </si>
@@ -1061,6 +1061,12 @@
   </si>
   <si>
     <t>2026-12-17</t>
+  </si>
+  <si>
+    <t>2026-12-18</t>
+  </si>
+  <si>
+    <t>Weihnachtsmarkt</t>
   </si>
   <si>
     <t>2027-01-05</t>
@@ -5535,7 +5541,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J108"/>
+  <dimension ref="A1:J109"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="13" style="5" customWidth="1"/>
@@ -7856,13 +7862,13 @@
         <v>347</v>
       </c>
       <c r="B73" t="s">
-        <v>138</v>
+        <v>320</v>
       </c>
       <c r="C73" t="s">
-        <v>171</v>
+        <v>8</v>
       </c>
       <c r="D73" t="s">
-        <v>310</v>
+        <v>8</v>
       </c>
       <c r="E73" t="s">
         <v>8</v>
@@ -7871,7 +7877,7 @@
         <v>8</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>8</v>
+        <v>348</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -7885,16 +7891,16 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B74" t="s">
         <v>138</v>
       </c>
       <c r="C74" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D74" t="s">
-        <v>279</v>
+        <v>310</v>
       </c>
       <c r="E74" t="s">
         <v>8</v>
@@ -7917,16 +7923,16 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B75" t="s">
         <v>138</v>
       </c>
       <c r="C75" t="s">
-        <v>44</v>
+        <v>168</v>
       </c>
       <c r="D75" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="E75" t="s">
         <v>8</v>
@@ -7949,16 +7955,16 @@
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B76" t="s">
         <v>138</v>
       </c>
       <c r="C76" t="s">
-        <v>166</v>
+        <v>44</v>
       </c>
       <c r="D76" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="E76" t="s">
         <v>8</v>
@@ -7981,16 +7987,16 @@
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B77" t="s">
         <v>138</v>
       </c>
       <c r="C77" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D77" t="s">
-        <v>310</v>
+        <v>288</v>
       </c>
       <c r="E77" t="s">
         <v>8</v>
@@ -8013,16 +8019,16 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B78" t="s">
         <v>138</v>
       </c>
       <c r="C78" t="s">
-        <v>72</v>
+        <v>171</v>
       </c>
       <c r="D78" t="s">
-        <v>353</v>
+        <v>310</v>
       </c>
       <c r="E78" t="s">
         <v>8</v>
@@ -8051,10 +8057,10 @@
         <v>138</v>
       </c>
       <c r="C79" t="s">
-        <v>171</v>
+        <v>72</v>
       </c>
       <c r="D79" t="s">
-        <v>310</v>
+        <v>355</v>
       </c>
       <c r="E79" t="s">
         <v>8</v>
@@ -8077,16 +8083,16 @@
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B80" t="s">
         <v>138</v>
       </c>
       <c r="C80" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D80" t="s">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="E80" t="s">
         <v>8</v>
@@ -8109,16 +8115,16 @@
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B81" t="s">
         <v>138</v>
       </c>
       <c r="C81" t="s">
-        <v>72</v>
+        <v>166</v>
       </c>
       <c r="D81" t="s">
-        <v>353</v>
+        <v>290</v>
       </c>
       <c r="E81" t="s">
         <v>8</v>
@@ -8141,16 +8147,16 @@
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B82" t="s">
-        <v>320</v>
+        <v>138</v>
       </c>
       <c r="C82" t="s">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="D82" t="s">
-        <v>8</v>
+        <v>355</v>
       </c>
       <c r="E82" t="s">
         <v>8</v>
@@ -8159,7 +8165,7 @@
         <v>8</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>321</v>
+        <v>8</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -8173,16 +8179,16 @@
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B83" t="s">
-        <v>138</v>
+        <v>320</v>
       </c>
       <c r="C83" t="s">
-        <v>166</v>
+        <v>8</v>
       </c>
       <c r="D83" t="s">
-        <v>288</v>
+        <v>8</v>
       </c>
       <c r="E83" t="s">
         <v>8</v>
@@ -8191,7 +8197,7 @@
         <v>8</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>8</v>
+        <v>321</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -8205,16 +8211,16 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B84" t="s">
         <v>138</v>
       </c>
       <c r="C84" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D84" t="s">
-        <v>310</v>
+        <v>288</v>
       </c>
       <c r="E84" t="s">
         <v>8</v>
@@ -8237,16 +8243,16 @@
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B85" t="s">
         <v>138</v>
       </c>
       <c r="C85" t="s">
-        <v>72</v>
+        <v>171</v>
       </c>
       <c r="D85" t="s">
-        <v>353</v>
+        <v>310</v>
       </c>
       <c r="E85" t="s">
         <v>8</v>
@@ -8269,16 +8275,16 @@
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B86" t="s">
         <v>138</v>
       </c>
       <c r="C86" t="s">
-        <v>166</v>
+        <v>72</v>
       </c>
       <c r="D86" t="s">
-        <v>290</v>
+        <v>355</v>
       </c>
       <c r="E86" t="s">
         <v>8</v>
@@ -8301,16 +8307,16 @@
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B87" t="s">
         <v>138</v>
       </c>
       <c r="C87" t="s">
-        <v>44</v>
+        <v>166</v>
       </c>
       <c r="D87" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="E87" t="s">
         <v>8</v>
@@ -8333,16 +8339,16 @@
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B88" t="s">
         <v>138</v>
       </c>
       <c r="C88" t="s">
-        <v>166</v>
+        <v>44</v>
       </c>
       <c r="D88" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="E88" t="s">
         <v>8</v>
@@ -8365,16 +8371,16 @@
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B89" t="s">
         <v>138</v>
       </c>
       <c r="C89" t="s">
-        <v>44</v>
+        <v>166</v>
       </c>
       <c r="D89" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="E89" t="s">
         <v>8</v>
@@ -8397,16 +8403,16 @@
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B90" t="s">
         <v>138</v>
       </c>
       <c r="C90" t="s">
-        <v>166</v>
+        <v>44</v>
       </c>
       <c r="D90" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="E90" t="s">
         <v>8</v>
@@ -8429,16 +8435,16 @@
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B91" t="s">
         <v>138</v>
       </c>
       <c r="C91" t="s">
-        <v>44</v>
+        <v>166</v>
       </c>
       <c r="D91" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="E91" t="s">
         <v>8</v>
@@ -8461,7 +8467,7 @@
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B92" t="s">
         <v>138</v>
@@ -8470,7 +8476,7 @@
         <v>44</v>
       </c>
       <c r="D92" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E92" t="s">
         <v>8</v>
@@ -8493,16 +8499,16 @@
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B93" t="s">
         <v>138</v>
       </c>
       <c r="C93" t="s">
-        <v>166</v>
+        <v>44</v>
       </c>
       <c r="D93" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="E93" t="s">
         <v>8</v>
@@ -8525,16 +8531,16 @@
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B94" t="s">
-        <v>320</v>
+        <v>138</v>
       </c>
       <c r="C94" t="s">
-        <v>8</v>
+        <v>166</v>
       </c>
       <c r="D94" t="s">
-        <v>8</v>
+        <v>288</v>
       </c>
       <c r="E94" t="s">
         <v>8</v>
@@ -8543,7 +8549,7 @@
         <v>8</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>321</v>
+        <v>8</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -8557,16 +8563,16 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B95" t="s">
-        <v>138</v>
+        <v>320</v>
       </c>
       <c r="C95" t="s">
-        <v>72</v>
+        <v>8</v>
       </c>
       <c r="D95" t="s">
-        <v>371</v>
+        <v>8</v>
       </c>
       <c r="E95" t="s">
         <v>8</v>
@@ -8575,7 +8581,7 @@
         <v>8</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>8</v>
+        <v>321</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -8595,10 +8601,10 @@
         <v>138</v>
       </c>
       <c r="C96" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="D96" t="s">
-        <v>282</v>
+        <v>373</v>
       </c>
       <c r="E96" t="s">
         <v>8</v>
@@ -8621,16 +8627,16 @@
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B97" t="s">
         <v>138</v>
       </c>
       <c r="C97" t="s">
-        <v>166</v>
+        <v>44</v>
       </c>
       <c r="D97" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="E97" t="s">
         <v>8</v>
@@ -8653,16 +8659,16 @@
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B98" t="s">
         <v>138</v>
       </c>
       <c r="C98" t="s">
-        <v>72</v>
+        <v>166</v>
       </c>
       <c r="D98" t="s">
-        <v>371</v>
+        <v>288</v>
       </c>
       <c r="E98" t="s">
         <v>8</v>
@@ -8685,16 +8691,16 @@
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B99" t="s">
-        <v>320</v>
+        <v>138</v>
       </c>
       <c r="C99" t="s">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="D99" t="s">
-        <v>8</v>
+        <v>373</v>
       </c>
       <c r="E99" t="s">
         <v>8</v>
@@ -8703,7 +8709,7 @@
         <v>8</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>376</v>
+        <v>8</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -8720,13 +8726,13 @@
         <v>377</v>
       </c>
       <c r="B100" t="s">
-        <v>138</v>
+        <v>320</v>
       </c>
       <c r="C100" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="D100" t="s">
-        <v>282</v>
+        <v>8</v>
       </c>
       <c r="E100" t="s">
         <v>8</v>
@@ -8735,7 +8741,7 @@
         <v>8</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>8</v>
+        <v>378</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -8749,16 +8755,16 @@
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B101" t="s">
         <v>138</v>
       </c>
       <c r="C101" t="s">
-        <v>166</v>
+        <v>44</v>
       </c>
       <c r="D101" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="E101" t="s">
         <v>8</v>
@@ -8781,16 +8787,16 @@
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B102" t="s">
         <v>138</v>
       </c>
       <c r="C102" t="s">
-        <v>72</v>
+        <v>166</v>
       </c>
       <c r="D102" t="s">
-        <v>371</v>
+        <v>288</v>
       </c>
       <c r="E102" t="s">
         <v>8</v>
@@ -8813,16 +8819,16 @@
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B103" t="s">
         <v>138</v>
       </c>
       <c r="C103" t="s">
-        <v>171</v>
+        <v>72</v>
       </c>
       <c r="D103" t="s">
-        <v>310</v>
+        <v>373</v>
       </c>
       <c r="E103" t="s">
         <v>8</v>
@@ -8845,16 +8851,16 @@
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B104" t="s">
         <v>138</v>
       </c>
       <c r="C104" t="s">
-        <v>44</v>
+        <v>171</v>
       </c>
       <c r="D104" t="s">
-        <v>284</v>
+        <v>310</v>
       </c>
       <c r="E104" t="s">
         <v>8</v>
@@ -8877,16 +8883,16 @@
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B105" t="s">
         <v>138</v>
       </c>
       <c r="C105" t="s">
-        <v>171</v>
+        <v>44</v>
       </c>
       <c r="D105" t="s">
-        <v>310</v>
+        <v>284</v>
       </c>
       <c r="E105" t="s">
         <v>8</v>
@@ -8909,16 +8915,16 @@
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B106" t="s">
         <v>138</v>
       </c>
       <c r="C106" t="s">
-        <v>44</v>
+        <v>171</v>
       </c>
       <c r="D106" t="s">
-        <v>284</v>
+        <v>310</v>
       </c>
       <c r="E106" t="s">
         <v>8</v>
@@ -8941,16 +8947,16 @@
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B107" t="s">
         <v>138</v>
       </c>
       <c r="C107" t="s">
-        <v>171</v>
+        <v>44</v>
       </c>
       <c r="D107" t="s">
-        <v>310</v>
+        <v>284</v>
       </c>
       <c r="E107" t="s">
         <v>8</v>
@@ -8973,33 +8979,65 @@
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" s="5" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B108" t="s">
         <v>138</v>
       </c>
       <c r="C108" t="s">
+        <v>171</v>
+      </c>
+      <c r="D108" t="s">
+        <v>310</v>
+      </c>
+      <c r="E108" t="s">
+        <v>8</v>
+      </c>
+      <c r="F108" t="s">
+        <v>8</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H108" t="s">
+        <v>8</v>
+      </c>
+      <c r="I108" t="s">
+        <v>8</v>
+      </c>
+      <c r="J108" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A109" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="B109" t="s">
+        <v>138</v>
+      </c>
+      <c r="C109" t="s">
         <v>44</v>
       </c>
-      <c r="D108" t="s">
+      <c r="D109" t="s">
         <v>284</v>
       </c>
-      <c r="E108" t="s">
-        <v>8</v>
-      </c>
-      <c r="F108" t="s">
-        <v>8</v>
-      </c>
-      <c r="G108" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H108" t="s">
-        <v>8</v>
-      </c>
-      <c r="I108" t="s">
-        <v>8</v>
-      </c>
-      <c r="J108" t="s">
+      <c r="E109" t="s">
+        <v>8</v>
+      </c>
+      <c r="F109" t="s">
+        <v>8</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H109" t="s">
+        <v>8</v>
+      </c>
+      <c r="I109" t="s">
+        <v>8</v>
+      </c>
+      <c r="J109" t="s">
         <v>8</v>
       </c>
     </row>

--- a/content/jahrgaenge/Jg7.xlsx
+++ b/content/jahrgaenge/Jg7.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1974" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2107" uniqueCount="443">
   <si>
     <t>Hinweise zu Jg7.xlsx</t>
   </si>
@@ -616,6 +616,18 @@
     <t>Fallbericht an das Gesundheitsamt</t>
   </si>
   <si>
+    <t>The Magic Mirror</t>
+  </si>
+  <si>
+    <t>design a reading journal</t>
+  </si>
+  <si>
+    <t>Orientierung auf der Erde</t>
+  </si>
+  <si>
+    <t>Anwenden des erlernten Wissens, um das ausgefallene Navigationssystem neu zu starten</t>
+  </si>
+  <si>
     <t>Die geheimnisvolle Welt der Balladen</t>
   </si>
   <si>
@@ -854,6 +866,159 @@
   </si>
   <si>
     <t>Läuft über 2 Termine à 90 Minuten.</t>
+  </si>
+  <si>
+    <t>What's a magic mirror?</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>Judging a Book by Its Cover</t>
+  </si>
+  <si>
+    <t>your book</t>
+  </si>
+  <si>
+    <t>Getting Started: How to Team Reader (2.1)</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>Getting Started: My Reading Journal (2.2)</t>
+  </si>
+  <si>
+    <t>The first part of the story</t>
+  </si>
+  <si>
+    <t>a laptop, A3</t>
+  </si>
+  <si>
+    <t>In the museum (4.1)</t>
+  </si>
+  <si>
+    <t>A4, A5</t>
+  </si>
+  <si>
+    <t>Museums (4.2)</t>
+  </si>
+  <si>
+    <t>a laptop</t>
+  </si>
+  <si>
+    <t>Travelling back in time – Ruby</t>
+  </si>
+  <si>
+    <t>A6</t>
+  </si>
+  <si>
+    <t>Travelling back in time – Noah</t>
+  </si>
+  <si>
+    <t>A7</t>
+  </si>
+  <si>
+    <t>Travelling back in time – Layla</t>
+  </si>
+  <si>
+    <t>A8</t>
+  </si>
+  <si>
+    <t>In the Tower</t>
+  </si>
+  <si>
+    <t>A9</t>
+  </si>
+  <si>
+    <t>Run, Ruby, Run!</t>
+  </si>
+  <si>
+    <t>A10</t>
+  </si>
+  <si>
+    <t>Visiting the market</t>
+  </si>
+  <si>
+    <t>A11</t>
+  </si>
+  <si>
+    <t>Medieval markets (10.1)</t>
+  </si>
+  <si>
+    <t>How to defeat the Spanish</t>
+  </si>
+  <si>
+    <t>A12</t>
+  </si>
+  <si>
+    <t>Getting back with a surprise</t>
+  </si>
+  <si>
+    <t>A13 / A 14 / A15</t>
+  </si>
+  <si>
+    <t>Leaving the Magic Mirror behind</t>
+  </si>
+  <si>
+    <t>A16 / A17 / A18, M4, M5</t>
+  </si>
+  <si>
+    <t>Das Gradnetz der Erde</t>
+  </si>
+  <si>
+    <t>M1 &amp; 2, A1 &amp; 2, Atlas</t>
+  </si>
+  <si>
+    <t>Geographische Koordinaten</t>
+  </si>
+  <si>
+    <t>M3, A3–6, Atlas</t>
+  </si>
+  <si>
+    <t>Wie weiß mein Handy, wo ich bin?</t>
+  </si>
+  <si>
+    <t>M4, A7, Atlas</t>
+  </si>
+  <si>
+    <t>Zeitzonen der Erde</t>
+  </si>
+  <si>
+    <t>M5, A8–11, Atlas</t>
+  </si>
+  <si>
+    <t>Beleuchtungszonen der Erde</t>
+  </si>
+  <si>
+    <t>A12–13, Laptop</t>
+  </si>
+  <si>
+    <t>Entstehung der Jahreszeiten</t>
+  </si>
+  <si>
+    <t>M6, A14–17</t>
+  </si>
+  <si>
+    <t>Schalenaufbau der Erde</t>
+  </si>
+  <si>
+    <t>M7, A18–19, Kleber &amp; Schere</t>
+  </si>
+  <si>
+    <t>Klimazonen und Klimadiagramme</t>
+  </si>
+  <si>
+    <t>A20–21, M8, Atlas</t>
+  </si>
+  <si>
+    <t>Warum lügen Weltkarten?</t>
+  </si>
+  <si>
+    <t>A22, Atlas</t>
+  </si>
+  <si>
+    <t>A23/0-5, Atlas</t>
   </si>
   <si>
     <t>2026-08-24</t>
@@ -3730,16 +3895,16 @@
         <v>166</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>198</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>8</v>
+        <v>199</v>
+      </c>
+      <c r="F3">
+        <v>17</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>8</v>
@@ -3756,16 +3921,16 @@
         <v>168</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8</v>
+        <v>200</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>8</v>
+        <v>201</v>
+      </c>
+      <c r="F4">
+        <v>10</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>8</v>
@@ -3782,13 +3947,13 @@
         <v>44</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F5" t="s">
         <v>8</v>
@@ -3808,13 +3973,13 @@
         <v>171</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F6">
         <v>13</v>
@@ -4224,7 +4389,7 @@
         <v>193</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>8</v>
@@ -4259,7 +4424,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -4304,7 +4469,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D2" t="s">
         <v>93</v>
@@ -4316,7 +4481,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>8</v>
@@ -4330,7 +4495,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="D3" t="s">
         <v>93</v>
@@ -4342,7 +4507,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>8</v>
@@ -4356,7 +4521,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="D4" t="s">
         <v>93</v>
@@ -4368,7 +4533,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>8</v>
@@ -4382,7 +4547,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="D5" t="s">
         <v>93</v>
@@ -4394,7 +4559,7 @@
         <v>2</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>8</v>
@@ -4408,7 +4573,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D6" t="s">
         <v>93</v>
@@ -4420,7 +4585,7 @@
         <v>2</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>8</v>
@@ -4434,10 +4599,10 @@
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="D7" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E7">
         <v>90</v>
@@ -4446,10 +4611,10 @@
         <v>2</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -4460,7 +4625,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D8" t="s">
         <v>93</v>
@@ -4472,7 +4637,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>8</v>
@@ -4486,10 +4651,10 @@
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D9" t="s">
         <v>215</v>
-      </c>
-      <c r="D9" t="s">
-        <v>211</v>
       </c>
       <c r="E9">
         <v>90</v>
@@ -4498,10 +4663,10 @@
         <v>2</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -4512,7 +4677,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D10" t="s">
         <v>93</v>
@@ -4524,7 +4689,7 @@
         <v>2</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>8</v>
@@ -4538,7 +4703,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D11" t="s">
         <v>93</v>
@@ -4550,7 +4715,7 @@
         <v>2</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>8</v>
@@ -4564,7 +4729,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D12" t="s">
         <v>93</v>
@@ -4576,7 +4741,7 @@
         <v>2</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>8</v>
@@ -4590,10 +4755,10 @@
         <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="D13" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E13">
         <v>60</v>
@@ -4602,10 +4767,10 @@
         <v>3</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -4616,7 +4781,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D14" t="s">
         <v>93</v>
@@ -4628,7 +4793,7 @@
         <v>3</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>8</v>
@@ -4642,7 +4807,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D15" t="s">
         <v>93</v>
@@ -4654,7 +4819,7 @@
         <v>2</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>8</v>
@@ -4668,7 +4833,7 @@
         <v>2</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D16" t="s">
         <v>93</v>
@@ -4680,7 +4845,7 @@
         <v>2</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>8</v>
@@ -4694,10 +4859,10 @@
         <v>3</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="D17" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E17">
         <v>40</v>
@@ -4706,10 +4871,10 @@
         <v>3</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -4720,10 +4885,10 @@
         <v>4</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="D18" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E18">
         <v>40</v>
@@ -4732,10 +4897,10 @@
         <v>3</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -4746,7 +4911,7 @@
         <v>5</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="D19" t="s">
         <v>93</v>
@@ -4758,7 +4923,7 @@
         <v>3</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>8</v>
@@ -4772,7 +4937,7 @@
         <v>6</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D20" t="s">
         <v>93</v>
@@ -4784,7 +4949,7 @@
         <v>3</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>8</v>
@@ -4798,7 +4963,7 @@
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="D21" t="s">
         <v>93</v>
@@ -4810,7 +4975,7 @@
         <v>2</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>8</v>
@@ -4824,10 +4989,10 @@
         <v>8</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D22" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E22">
         <v>40</v>
@@ -4836,10 +5001,10 @@
         <v>2</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -4850,7 +5015,7 @@
         <v>9</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D23" t="s">
         <v>93</v>
@@ -4862,7 +5027,7 @@
         <v>3</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>8</v>
@@ -4876,7 +5041,7 @@
         <v>10</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D24" t="s">
         <v>93</v>
@@ -4888,7 +5053,7 @@
         <v>1</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>8</v>
@@ -4902,10 +5067,10 @@
         <v>11</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D25" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E25">
         <v>40</v>
@@ -4914,10 +5079,10 @@
         <v>3</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -4928,7 +5093,7 @@
         <v>12</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D26" t="s">
         <v>93</v>
@@ -4940,7 +5105,7 @@
         <v>3</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>8</v>
@@ -4954,10 +5119,10 @@
         <v>13</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D27" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E27">
         <v>30</v>
@@ -4966,10 +5131,10 @@
         <v>2</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -4980,10 +5145,10 @@
         <v>14</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D28" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E28">
         <v>30</v>
@@ -4992,10 +5157,10 @@
         <v>2</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -5006,10 +5171,10 @@
         <v>1</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D29" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E29">
         <v>10</v>
@@ -5018,10 +5183,10 @@
         <v>1</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -5032,7 +5197,7 @@
         <v>2</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D30" t="s">
         <v>93</v>
@@ -5044,7 +5209,7 @@
         <v>2</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>8</v>
@@ -5058,7 +5223,7 @@
         <v>3</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="D31" t="s">
         <v>93</v>
@@ -5070,7 +5235,7 @@
         <v>2</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>8</v>
@@ -5084,7 +5249,7 @@
         <v>4</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D32" t="s">
         <v>93</v>
@@ -5096,7 +5261,7 @@
         <v>3</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>8</v>
@@ -5110,7 +5275,7 @@
         <v>5</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="D33" t="s">
         <v>93</v>
@@ -5122,7 +5287,7 @@
         <v>2</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>8</v>
@@ -5136,7 +5301,7 @@
         <v>6</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="D34" t="s">
         <v>93</v>
@@ -5148,7 +5313,7 @@
         <v>3</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>8</v>
@@ -5162,7 +5327,7 @@
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D35" t="s">
         <v>93</v>
@@ -5174,7 +5339,7 @@
         <v>1</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>8</v>
@@ -5188,10 +5353,10 @@
         <v>8</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D36" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E36">
         <v>15</v>
@@ -5200,10 +5365,10 @@
         <v>1</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -5214,7 +5379,7 @@
         <v>9</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D37" t="s">
         <v>93</v>
@@ -5226,7 +5391,7 @@
         <v>3</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>8</v>
@@ -5240,7 +5405,7 @@
         <v>10</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D38" t="s">
         <v>93</v>
@@ -5252,7 +5417,7 @@
         <v>2</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>8</v>
@@ -5266,10 +5431,10 @@
         <v>11</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D39" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E39">
         <v>10</v>
@@ -5278,10 +5443,10 @@
         <v>1</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
@@ -5292,7 +5457,7 @@
         <v>12</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D40" t="s">
         <v>93</v>
@@ -5304,7 +5469,7 @@
         <v>2</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>8</v>
@@ -5318,10 +5483,10 @@
         <v>13</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D41" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E41">
         <v>10</v>
@@ -5330,10 +5495,10 @@
         <v>1</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -5344,7 +5509,7 @@
         <v>14</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="D42" t="s">
         <v>93</v>
@@ -5356,7 +5521,7 @@
         <v>2</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>8</v>
@@ -5370,10 +5535,10 @@
         <v>15</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="D43" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E43">
         <v>45</v>
@@ -5382,10 +5547,10 @@
         <v>1</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
@@ -5396,7 +5561,7 @@
         <v>16</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D44" t="s">
         <v>93</v>
@@ -5408,10 +5573,712 @@
         <v>3</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>165</v>
+      </c>
+      <c r="B45">
+        <v>1</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="D45" t="s">
+        <v>93</v>
+      </c>
+      <c r="E45">
+        <v>45</v>
+      </c>
+      <c r="F45">
+        <v>1</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>165</v>
+      </c>
+      <c r="B46">
+        <v>2</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D46" t="s">
+        <v>93</v>
+      </c>
+      <c r="E46">
+        <v>15</v>
+      </c>
+      <c r="F46">
+        <v>1</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>165</v>
+      </c>
+      <c r="B47">
+        <v>3</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D47" t="s">
+        <v>93</v>
+      </c>
+      <c r="E47">
+        <v>20</v>
+      </c>
+      <c r="F47">
+        <v>1</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>165</v>
+      </c>
+      <c r="B48">
+        <v>4</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D48" t="s">
+        <v>93</v>
+      </c>
+      <c r="E48">
+        <v>10</v>
+      </c>
+      <c r="F48">
+        <v>1</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>165</v>
+      </c>
+      <c r="B49">
+        <v>5</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="D49" t="s">
+        <v>93</v>
+      </c>
+      <c r="E49">
+        <v>90</v>
+      </c>
+      <c r="F49">
+        <v>1</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>165</v>
+      </c>
+      <c r="B50">
+        <v>6</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="D50" t="s">
+        <v>93</v>
+      </c>
+      <c r="E50">
+        <v>70</v>
+      </c>
+      <c r="F50">
+        <v>1</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>165</v>
+      </c>
+      <c r="B51">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="D51" t="s">
+        <v>215</v>
+      </c>
+      <c r="E51">
+        <v>90</v>
+      </c>
+      <c r="F51">
+        <v>2</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>165</v>
+      </c>
+      <c r="B52">
+        <v>8</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="D52" t="s">
+        <v>93</v>
+      </c>
+      <c r="E52">
+        <v>90</v>
+      </c>
+      <c r="F52">
+        <v>2</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>165</v>
+      </c>
+      <c r="B53">
+        <v>9</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D53" t="s">
+        <v>93</v>
+      </c>
+      <c r="E53">
+        <v>90</v>
+      </c>
+      <c r="F53">
+        <v>1</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>165</v>
+      </c>
+      <c r="B54">
+        <v>10</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="D54" t="s">
+        <v>93</v>
+      </c>
+      <c r="E54">
+        <v>90</v>
+      </c>
+      <c r="F54">
+        <v>3</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>165</v>
+      </c>
+      <c r="B55">
+        <v>11</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D55" t="s">
+        <v>93</v>
+      </c>
+      <c r="E55">
+        <v>120</v>
+      </c>
+      <c r="F55">
+        <v>1</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>165</v>
+      </c>
+      <c r="B56">
+        <v>12</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="D56" t="s">
+        <v>93</v>
+      </c>
+      <c r="E56">
+        <v>90</v>
+      </c>
+      <c r="F56">
+        <v>2</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>165</v>
+      </c>
+      <c r="B57">
+        <v>13</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="D57" t="s">
+        <v>93</v>
+      </c>
+      <c r="E57">
+        <v>90</v>
+      </c>
+      <c r="F57">
+        <v>1</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>165</v>
+      </c>
+      <c r="B58">
+        <v>14</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="D58" t="s">
+        <v>215</v>
+      </c>
+      <c r="E58">
+        <v>50</v>
+      </c>
+      <c r="F58">
+        <v>2</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>165</v>
+      </c>
+      <c r="B59">
+        <v>15</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D59" t="s">
+        <v>93</v>
+      </c>
+      <c r="E59">
+        <v>90</v>
+      </c>
+      <c r="F59">
+        <v>3</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>165</v>
+      </c>
+      <c r="B60">
+        <v>16</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="D60" t="s">
+        <v>93</v>
+      </c>
+      <c r="E60">
+        <v>90</v>
+      </c>
+      <c r="F60">
+        <v>2</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>165</v>
+      </c>
+      <c r="B61">
+        <v>17</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="D61" t="s">
+        <v>93</v>
+      </c>
+      <c r="E61">
+        <v>180</v>
+      </c>
+      <c r="F61">
+        <v>3</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>167</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D62" t="s">
+        <v>93</v>
+      </c>
+      <c r="E62">
+        <v>65</v>
+      </c>
+      <c r="F62">
+        <v>1</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>167</v>
+      </c>
+      <c r="B63">
+        <v>2</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="D63" t="s">
+        <v>93</v>
+      </c>
+      <c r="E63">
+        <v>90</v>
+      </c>
+      <c r="F63">
+        <v>2</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>167</v>
+      </c>
+      <c r="B64">
+        <v>3</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="D64" t="s">
+        <v>215</v>
+      </c>
+      <c r="E64">
+        <v>20</v>
+      </c>
+      <c r="F64">
+        <v>2</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>167</v>
+      </c>
+      <c r="B65">
+        <v>4</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D65" t="s">
+        <v>93</v>
+      </c>
+      <c r="E65">
+        <v>115</v>
+      </c>
+      <c r="F65">
+        <v>2</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>167</v>
+      </c>
+      <c r="B66">
+        <v>5</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="D66" t="s">
+        <v>93</v>
+      </c>
+      <c r="E66">
+        <v>40</v>
+      </c>
+      <c r="F66">
+        <v>1</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>167</v>
+      </c>
+      <c r="B67">
+        <v>6</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="D67" t="s">
+        <v>93</v>
+      </c>
+      <c r="E67">
+        <v>110</v>
+      </c>
+      <c r="F67">
+        <v>2</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>167</v>
+      </c>
+      <c r="B68">
+        <v>7</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="D68" t="s">
+        <v>93</v>
+      </c>
+      <c r="E68">
+        <v>50</v>
+      </c>
+      <c r="F68">
+        <v>1</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>167</v>
+      </c>
+      <c r="B69">
+        <v>8</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="D69" t="s">
+        <v>93</v>
+      </c>
+      <c r="E69">
+        <v>120</v>
+      </c>
+      <c r="F69">
+        <v>2</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>167</v>
+      </c>
+      <c r="B70">
+        <v>9</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="D70" t="s">
+        <v>215</v>
+      </c>
+      <c r="E70">
+        <v>30</v>
+      </c>
+      <c r="F70">
+        <v>2</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>167</v>
+      </c>
+      <c r="B71">
+        <v>10</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D71" t="s">
+        <v>93</v>
+      </c>
+      <c r="E71">
+        <v>90</v>
+      </c>
+      <c r="F71">
+        <v>2</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5587,7 +6454,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>278</v>
+        <v>333</v>
       </c>
       <c r="B2" t="s">
         <v>138</v>
@@ -5596,7 +6463,7 @@
         <v>168</v>
       </c>
       <c r="D2" t="s">
-        <v>279</v>
+        <v>334</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -5605,7 +6472,7 @@
         <v>8</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>280</v>
+        <v>335</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -5619,16 +6486,16 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>278</v>
+        <v>333</v>
       </c>
       <c r="B3" t="s">
-        <v>281</v>
+        <v>336</v>
       </c>
       <c r="C3" t="s">
         <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>282</v>
+        <v>337</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -5651,16 +6518,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>283</v>
+        <v>338</v>
       </c>
       <c r="B4" t="s">
-        <v>281</v>
+        <v>336</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>284</v>
+        <v>339</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -5683,7 +6550,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>285</v>
+        <v>340</v>
       </c>
       <c r="B5" t="s">
         <v>138</v>
@@ -5692,7 +6559,7 @@
         <v>166</v>
       </c>
       <c r="D5" t="s">
-        <v>286</v>
+        <v>341</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -5701,7 +6568,7 @@
         <v>8</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>287</v>
+        <v>342</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -5715,16 +6582,16 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>285</v>
+        <v>340</v>
       </c>
       <c r="B6" t="s">
-        <v>281</v>
+        <v>336</v>
       </c>
       <c r="C6" t="s">
         <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>288</v>
+        <v>343</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -5747,16 +6614,16 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>289</v>
+        <v>344</v>
       </c>
       <c r="B7" t="s">
-        <v>281</v>
+        <v>336</v>
       </c>
       <c r="C7" t="s">
         <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>290</v>
+        <v>345</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -5779,7 +6646,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>291</v>
+        <v>346</v>
       </c>
       <c r="B8" t="s">
         <v>138</v>
@@ -5797,7 +6664,7 @@
         <v>8</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>292</v>
+        <v>347</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -5820,7 +6687,7 @@
         <v>168</v>
       </c>
       <c r="D9" t="s">
-        <v>279</v>
+        <v>334</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -5829,7 +6696,7 @@
         <v>8</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>293</v>
+        <v>348</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -5846,13 +6713,13 @@
         <v>56</v>
       </c>
       <c r="B10" t="s">
-        <v>281</v>
+        <v>336</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>282</v>
+        <v>337</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -5875,16 +6742,16 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>294</v>
+        <v>349</v>
       </c>
       <c r="B11" t="s">
-        <v>281</v>
+        <v>336</v>
       </c>
       <c r="C11" t="s">
         <v>8</v>
       </c>
       <c r="D11" t="s">
-        <v>284</v>
+        <v>339</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -5907,7 +6774,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>295</v>
+        <v>350</v>
       </c>
       <c r="B12" t="s">
         <v>138</v>
@@ -5916,7 +6783,7 @@
         <v>166</v>
       </c>
       <c r="D12" t="s">
-        <v>286</v>
+        <v>341</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -5925,7 +6792,7 @@
         <v>8</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>296</v>
+        <v>351</v>
       </c>
       <c r="H12">
         <v>13</v>
@@ -5939,16 +6806,16 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>295</v>
+        <v>350</v>
       </c>
       <c r="B13" t="s">
-        <v>281</v>
+        <v>336</v>
       </c>
       <c r="C13" t="s">
         <v>8</v>
       </c>
       <c r="D13" t="s">
-        <v>288</v>
+        <v>343</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -5971,16 +6838,16 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>297</v>
+        <v>352</v>
       </c>
       <c r="B14" t="s">
-        <v>281</v>
+        <v>336</v>
       </c>
       <c r="C14" t="s">
         <v>8</v>
       </c>
       <c r="D14" t="s">
-        <v>290</v>
+        <v>345</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -6003,7 +6870,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>298</v>
+        <v>353</v>
       </c>
       <c r="B15" t="s">
         <v>138</v>
@@ -6021,7 +6888,7 @@
         <v>8</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>299</v>
+        <v>354</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -6035,16 +6902,16 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>298</v>
+        <v>353</v>
       </c>
       <c r="B16" t="s">
-        <v>281</v>
+        <v>336</v>
       </c>
       <c r="C16" t="s">
         <v>8</v>
       </c>
       <c r="D16" t="s">
-        <v>286</v>
+        <v>341</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -6076,7 +6943,7 @@
         <v>168</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>334</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -6085,7 +6952,7 @@
         <v>8</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>300</v>
+        <v>355</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -6102,13 +6969,13 @@
         <v>127</v>
       </c>
       <c r="B18" t="s">
-        <v>281</v>
+        <v>336</v>
       </c>
       <c r="C18" t="s">
         <v>8</v>
       </c>
       <c r="D18" t="s">
-        <v>282</v>
+        <v>337</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -6134,13 +7001,13 @@
         <v>136</v>
       </c>
       <c r="B19" t="s">
-        <v>281</v>
+        <v>336</v>
       </c>
       <c r="C19" t="s">
         <v>8</v>
       </c>
       <c r="D19" t="s">
-        <v>284</v>
+        <v>339</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -6163,7 +7030,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>301</v>
+        <v>356</v>
       </c>
       <c r="B20" t="s">
         <v>138</v>
@@ -6172,7 +7039,7 @@
         <v>166</v>
       </c>
       <c r="D20" t="s">
-        <v>286</v>
+        <v>341</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -6181,7 +7048,7 @@
         <v>8</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>302</v>
+        <v>357</v>
       </c>
       <c r="H20">
         <v>12</v>
@@ -6195,16 +7062,16 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>301</v>
+        <v>356</v>
       </c>
       <c r="B21" t="s">
-        <v>281</v>
+        <v>336</v>
       </c>
       <c r="C21" t="s">
         <v>8</v>
       </c>
       <c r="D21" t="s">
-        <v>288</v>
+        <v>343</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -6227,16 +7094,16 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>303</v>
+        <v>358</v>
       </c>
       <c r="B22" t="s">
-        <v>281</v>
+        <v>336</v>
       </c>
       <c r="C22" t="s">
         <v>8</v>
       </c>
       <c r="D22" t="s">
-        <v>290</v>
+        <v>345</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -6259,7 +7126,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>304</v>
+        <v>359</v>
       </c>
       <c r="B23" t="s">
         <v>138</v>
@@ -6277,7 +7144,7 @@
         <v>8</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>305</v>
+        <v>360</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -6291,16 +7158,16 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>304</v>
+        <v>359</v>
       </c>
       <c r="B24" t="s">
-        <v>281</v>
+        <v>336</v>
       </c>
       <c r="C24" t="s">
         <v>8</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>341</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -6323,16 +7190,16 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>306</v>
+        <v>361</v>
       </c>
       <c r="B25" t="s">
-        <v>281</v>
+        <v>336</v>
       </c>
       <c r="C25" t="s">
         <v>8</v>
       </c>
       <c r="D25" t="s">
-        <v>279</v>
+        <v>334</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -6355,16 +7222,16 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>307</v>
+        <v>362</v>
       </c>
       <c r="B26" t="s">
-        <v>281</v>
+        <v>336</v>
       </c>
       <c r="C26" t="s">
         <v>8</v>
       </c>
       <c r="D26" t="s">
-        <v>286</v>
+        <v>341</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -6387,16 +7254,16 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>308</v>
+        <v>363</v>
       </c>
       <c r="B27" t="s">
-        <v>281</v>
+        <v>336</v>
       </c>
       <c r="C27" t="s">
         <v>8</v>
       </c>
       <c r="D27" t="s">
-        <v>279</v>
+        <v>334</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -6419,7 +7286,7 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>309</v>
+        <v>364</v>
       </c>
       <c r="B28" t="s">
         <v>138</v>
@@ -6428,7 +7295,7 @@
         <v>171</v>
       </c>
       <c r="D28" t="s">
-        <v>310</v>
+        <v>365</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -6451,16 +7318,16 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>311</v>
+        <v>366</v>
       </c>
       <c r="B29" t="s">
-        <v>281</v>
+        <v>336</v>
       </c>
       <c r="C29" t="s">
         <v>8</v>
       </c>
       <c r="D29" t="s">
-        <v>286</v>
+        <v>341</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -6483,7 +7350,7 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>312</v>
+        <v>367</v>
       </c>
       <c r="B30" t="s">
         <v>138</v>
@@ -6492,7 +7359,7 @@
         <v>44</v>
       </c>
       <c r="D30" t="s">
-        <v>284</v>
+        <v>339</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -6515,16 +7382,16 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>312</v>
+        <v>367</v>
       </c>
       <c r="B31" t="s">
-        <v>281</v>
+        <v>336</v>
       </c>
       <c r="C31" t="s">
         <v>8</v>
       </c>
       <c r="D31" t="s">
-        <v>290</v>
+        <v>345</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -6565,7 +7432,7 @@
         <v>8</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>313</v>
+        <v>368</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -6582,13 +7449,13 @@
         <v>58</v>
       </c>
       <c r="B33" t="s">
-        <v>281</v>
+        <v>336</v>
       </c>
       <c r="C33" t="s">
         <v>8</v>
       </c>
       <c r="D33" t="s">
-        <v>288</v>
+        <v>343</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -6611,16 +7478,16 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>314</v>
+        <v>369</v>
       </c>
       <c r="B34" t="s">
-        <v>281</v>
+        <v>336</v>
       </c>
       <c r="C34" t="s">
         <v>8</v>
       </c>
       <c r="D34" t="s">
-        <v>279</v>
+        <v>334</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -6643,7 +7510,7 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>315</v>
+        <v>370</v>
       </c>
       <c r="B35" t="s">
         <v>138</v>
@@ -6652,7 +7519,7 @@
         <v>171</v>
       </c>
       <c r="D35" t="s">
-        <v>310</v>
+        <v>365</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -6675,16 +7542,16 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>316</v>
+        <v>371</v>
       </c>
       <c r="B36" t="s">
-        <v>281</v>
+        <v>336</v>
       </c>
       <c r="C36" t="s">
         <v>8</v>
       </c>
       <c r="D36" t="s">
-        <v>279</v>
+        <v>334</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
@@ -6707,7 +7574,7 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>317</v>
+        <v>372</v>
       </c>
       <c r="B37" t="s">
         <v>138</v>
@@ -6716,7 +7583,7 @@
         <v>44</v>
       </c>
       <c r="D37" t="s">
-        <v>284</v>
+        <v>339</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
@@ -6739,16 +7606,16 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>317</v>
+        <v>372</v>
       </c>
       <c r="B38" t="s">
-        <v>281</v>
+        <v>336</v>
       </c>
       <c r="C38" t="s">
         <v>8</v>
       </c>
       <c r="D38" t="s">
-        <v>290</v>
+        <v>345</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
@@ -6771,7 +7638,7 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>318</v>
+        <v>373</v>
       </c>
       <c r="B39" t="s">
         <v>138</v>
@@ -6789,7 +7656,7 @@
         <v>8</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>319</v>
+        <v>374</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -6803,16 +7670,16 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>318</v>
+        <v>373</v>
       </c>
       <c r="B40" t="s">
-        <v>281</v>
+        <v>336</v>
       </c>
       <c r="C40" t="s">
         <v>8</v>
       </c>
       <c r="D40" t="s">
-        <v>288</v>
+        <v>343</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
@@ -6838,7 +7705,7 @@
         <v>20</v>
       </c>
       <c r="B41" t="s">
-        <v>320</v>
+        <v>375</v>
       </c>
       <c r="C41" t="s">
         <v>8</v>
@@ -6853,7 +7720,7 @@
         <v>8</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>321</v>
+        <v>376</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -6867,7 +7734,7 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>322</v>
+        <v>377</v>
       </c>
       <c r="B42" t="s">
         <v>138</v>
@@ -6876,7 +7743,7 @@
         <v>171</v>
       </c>
       <c r="D42" t="s">
-        <v>310</v>
+        <v>365</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
@@ -6899,16 +7766,16 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>323</v>
+        <v>378</v>
       </c>
       <c r="B43" t="s">
-        <v>281</v>
+        <v>336</v>
       </c>
       <c r="C43" t="s">
         <v>8</v>
       </c>
       <c r="D43" t="s">
-        <v>279</v>
+        <v>334</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
@@ -6931,7 +7798,7 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>324</v>
+        <v>379</v>
       </c>
       <c r="B44" t="s">
         <v>138</v>
@@ -6940,7 +7807,7 @@
         <v>44</v>
       </c>
       <c r="D44" t="s">
-        <v>284</v>
+        <v>339</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
@@ -6963,16 +7830,16 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>324</v>
+        <v>379</v>
       </c>
       <c r="B45" t="s">
-        <v>281</v>
+        <v>336</v>
       </c>
       <c r="C45" t="s">
         <v>8</v>
       </c>
       <c r="D45" t="s">
-        <v>290</v>
+        <v>345</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -6995,7 +7862,7 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>325</v>
+        <v>380</v>
       </c>
       <c r="B46" t="s">
         <v>138</v>
@@ -7013,7 +7880,7 @@
         <v>8</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>326</v>
+        <v>381</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -7027,16 +7894,16 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>325</v>
+        <v>380</v>
       </c>
       <c r="B47" t="s">
-        <v>281</v>
+        <v>336</v>
       </c>
       <c r="C47" t="s">
         <v>8</v>
       </c>
       <c r="D47" t="s">
-        <v>288</v>
+        <v>343</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
@@ -7059,16 +7926,16 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>327</v>
+        <v>382</v>
       </c>
       <c r="B48" t="s">
-        <v>281</v>
+        <v>336</v>
       </c>
       <c r="C48" t="s">
         <v>8</v>
       </c>
       <c r="D48" t="s">
-        <v>279</v>
+        <v>334</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
@@ -7091,16 +7958,16 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>328</v>
+        <v>383</v>
       </c>
       <c r="B49" t="s">
-        <v>281</v>
+        <v>336</v>
       </c>
       <c r="C49" t="s">
         <v>8</v>
       </c>
       <c r="D49" t="s">
-        <v>282</v>
+        <v>337</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
@@ -7123,7 +7990,7 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>329</v>
+        <v>384</v>
       </c>
       <c r="B50" t="s">
         <v>138</v>
@@ -7132,7 +7999,7 @@
         <v>168</v>
       </c>
       <c r="D50" t="s">
-        <v>279</v>
+        <v>334</v>
       </c>
       <c r="E50" t="s">
         <v>8</v>
@@ -7155,16 +8022,16 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>329</v>
+        <v>384</v>
       </c>
       <c r="B51" t="s">
-        <v>281</v>
+        <v>336</v>
       </c>
       <c r="C51" t="s">
         <v>8</v>
       </c>
       <c r="D51" t="s">
-        <v>286</v>
+        <v>341</v>
       </c>
       <c r="E51" t="s">
         <v>8</v>
@@ -7187,7 +8054,7 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>330</v>
+        <v>385</v>
       </c>
       <c r="B52" t="s">
         <v>138</v>
@@ -7196,7 +8063,7 @@
         <v>166</v>
       </c>
       <c r="D52" t="s">
-        <v>290</v>
+        <v>345</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
@@ -7219,16 +8086,16 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>330</v>
+        <v>385</v>
       </c>
       <c r="B53" t="s">
-        <v>281</v>
+        <v>336</v>
       </c>
       <c r="C53" t="s">
         <v>8</v>
       </c>
       <c r="D53" t="s">
-        <v>284</v>
+        <v>339</v>
       </c>
       <c r="E53" t="s">
         <v>8</v>
@@ -7251,16 +8118,16 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>331</v>
+        <v>386</v>
       </c>
       <c r="B54" t="s">
-        <v>281</v>
+        <v>336</v>
       </c>
       <c r="C54" t="s">
         <v>8</v>
       </c>
       <c r="D54" t="s">
-        <v>286</v>
+        <v>341</v>
       </c>
       <c r="E54" t="s">
         <v>8</v>
@@ -7283,16 +8150,16 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>332</v>
+        <v>387</v>
       </c>
       <c r="B55" t="s">
-        <v>281</v>
+        <v>336</v>
       </c>
       <c r="C55" t="s">
         <v>8</v>
       </c>
       <c r="D55" t="s">
-        <v>282</v>
+        <v>337</v>
       </c>
       <c r="E55" t="s">
         <v>8</v>
@@ -7315,7 +8182,7 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>333</v>
+        <v>388</v>
       </c>
       <c r="B56" t="s">
         <v>138</v>
@@ -7347,7 +8214,7 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>334</v>
+        <v>389</v>
       </c>
       <c r="B57" t="s">
         <v>138</v>
@@ -7356,7 +8223,7 @@
         <v>168</v>
       </c>
       <c r="D57" t="s">
-        <v>279</v>
+        <v>334</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
@@ -7379,7 +8246,7 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>335</v>
+        <v>390</v>
       </c>
       <c r="B58" t="s">
         <v>138</v>
@@ -7388,7 +8255,7 @@
         <v>166</v>
       </c>
       <c r="D58" t="s">
-        <v>290</v>
+        <v>345</v>
       </c>
       <c r="E58" t="s">
         <v>8</v>
@@ -7411,16 +8278,16 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>335</v>
+        <v>390</v>
       </c>
       <c r="B59" t="s">
-        <v>281</v>
+        <v>336</v>
       </c>
       <c r="C59" t="s">
         <v>8</v>
       </c>
       <c r="D59" t="s">
-        <v>284</v>
+        <v>339</v>
       </c>
       <c r="E59" t="s">
         <v>8</v>
@@ -7443,16 +8310,16 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="B60" t="s">
         <v>336</v>
       </c>
-      <c r="B60" t="s">
-        <v>281</v>
-      </c>
       <c r="C60" t="s">
         <v>8</v>
       </c>
       <c r="D60" t="s">
-        <v>282</v>
+        <v>337</v>
       </c>
       <c r="E60" t="s">
         <v>8</v>
@@ -7475,7 +8342,7 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>337</v>
+        <v>392</v>
       </c>
       <c r="B61" t="s">
         <v>138</v>
@@ -7507,7 +8374,7 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>338</v>
+        <v>393</v>
       </c>
       <c r="B62" t="s">
         <v>138</v>
@@ -7516,7 +8383,7 @@
         <v>168</v>
       </c>
       <c r="D62" t="s">
-        <v>279</v>
+        <v>334</v>
       </c>
       <c r="E62" t="s">
         <v>8</v>
@@ -7539,16 +8406,16 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>338</v>
+        <v>393</v>
       </c>
       <c r="B63" t="s">
-        <v>281</v>
+        <v>336</v>
       </c>
       <c r="C63" t="s">
         <v>8</v>
       </c>
       <c r="D63" t="s">
-        <v>286</v>
+        <v>341</v>
       </c>
       <c r="E63" t="s">
         <v>8</v>
@@ -7571,7 +8438,7 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>339</v>
+        <v>394</v>
       </c>
       <c r="B64" t="s">
         <v>138</v>
@@ -7580,7 +8447,7 @@
         <v>166</v>
       </c>
       <c r="D64" t="s">
-        <v>290</v>
+        <v>345</v>
       </c>
       <c r="E64" t="s">
         <v>8</v>
@@ -7603,16 +8470,16 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="B65" t="s">
+        <v>336</v>
+      </c>
+      <c r="C65" t="s">
+        <v>8</v>
+      </c>
+      <c r="D65" t="s">
         <v>339</v>
-      </c>
-      <c r="B65" t="s">
-        <v>281</v>
-      </c>
-      <c r="C65" t="s">
-        <v>8</v>
-      </c>
-      <c r="D65" t="s">
-        <v>284</v>
       </c>
       <c r="E65" t="s">
         <v>8</v>
@@ -7635,7 +8502,7 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>340</v>
+        <v>395</v>
       </c>
       <c r="B66" t="s">
         <v>138</v>
@@ -7667,7 +8534,7 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>341</v>
+        <v>396</v>
       </c>
       <c r="B67" t="s">
         <v>138</v>
@@ -7676,7 +8543,7 @@
         <v>171</v>
       </c>
       <c r="D67" t="s">
-        <v>310</v>
+        <v>365</v>
       </c>
       <c r="E67" t="s">
         <v>8</v>
@@ -7699,7 +8566,7 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>342</v>
+        <v>397</v>
       </c>
       <c r="B68" t="s">
         <v>138</v>
@@ -7708,7 +8575,7 @@
         <v>168</v>
       </c>
       <c r="D68" t="s">
-        <v>279</v>
+        <v>334</v>
       </c>
       <c r="E68" t="s">
         <v>8</v>
@@ -7731,7 +8598,7 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>343</v>
+        <v>398</v>
       </c>
       <c r="B69" t="s">
         <v>138</v>
@@ -7740,7 +8607,7 @@
         <v>44</v>
       </c>
       <c r="D69" t="s">
-        <v>282</v>
+        <v>337</v>
       </c>
       <c r="E69" t="s">
         <v>8</v>
@@ -7763,7 +8630,7 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>344</v>
+        <v>399</v>
       </c>
       <c r="B70" t="s">
         <v>138</v>
@@ -7772,7 +8639,7 @@
         <v>171</v>
       </c>
       <c r="D70" t="s">
-        <v>310</v>
+        <v>365</v>
       </c>
       <c r="E70" t="s">
         <v>8</v>
@@ -7795,7 +8662,7 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>345</v>
+        <v>400</v>
       </c>
       <c r="B71" t="s">
         <v>138</v>
@@ -7804,7 +8671,7 @@
         <v>168</v>
       </c>
       <c r="D71" t="s">
-        <v>279</v>
+        <v>334</v>
       </c>
       <c r="E71" t="s">
         <v>8</v>
@@ -7827,7 +8694,7 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>346</v>
+        <v>401</v>
       </c>
       <c r="B72" t="s">
         <v>138</v>
@@ -7836,7 +8703,7 @@
         <v>44</v>
       </c>
       <c r="D72" t="s">
-        <v>282</v>
+        <v>337</v>
       </c>
       <c r="E72" t="s">
         <v>8</v>
@@ -7859,10 +8726,10 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>347</v>
+        <v>402</v>
       </c>
       <c r="B73" t="s">
-        <v>320</v>
+        <v>375</v>
       </c>
       <c r="C73" t="s">
         <v>8</v>
@@ -7877,7 +8744,7 @@
         <v>8</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>348</v>
+        <v>403</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -7891,7 +8758,7 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>349</v>
+        <v>404</v>
       </c>
       <c r="B74" t="s">
         <v>138</v>
@@ -7900,7 +8767,7 @@
         <v>171</v>
       </c>
       <c r="D74" t="s">
-        <v>310</v>
+        <v>365</v>
       </c>
       <c r="E74" t="s">
         <v>8</v>
@@ -7923,7 +8790,7 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>350</v>
+        <v>405</v>
       </c>
       <c r="B75" t="s">
         <v>138</v>
@@ -7932,7 +8799,7 @@
         <v>168</v>
       </c>
       <c r="D75" t="s">
-        <v>279</v>
+        <v>334</v>
       </c>
       <c r="E75" t="s">
         <v>8</v>
@@ -7955,7 +8822,7 @@
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>351</v>
+        <v>406</v>
       </c>
       <c r="B76" t="s">
         <v>138</v>
@@ -7964,7 +8831,7 @@
         <v>44</v>
       </c>
       <c r="D76" t="s">
-        <v>282</v>
+        <v>337</v>
       </c>
       <c r="E76" t="s">
         <v>8</v>
@@ -7987,7 +8854,7 @@
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>352</v>
+        <v>407</v>
       </c>
       <c r="B77" t="s">
         <v>138</v>
@@ -7996,7 +8863,7 @@
         <v>166</v>
       </c>
       <c r="D77" t="s">
-        <v>288</v>
+        <v>343</v>
       </c>
       <c r="E77" t="s">
         <v>8</v>
@@ -8019,7 +8886,7 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>353</v>
+        <v>408</v>
       </c>
       <c r="B78" t="s">
         <v>138</v>
@@ -8028,7 +8895,7 @@
         <v>171</v>
       </c>
       <c r="D78" t="s">
-        <v>310</v>
+        <v>365</v>
       </c>
       <c r="E78" t="s">
         <v>8</v>
@@ -8051,7 +8918,7 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>354</v>
+        <v>409</v>
       </c>
       <c r="B79" t="s">
         <v>138</v>
@@ -8060,7 +8927,7 @@
         <v>72</v>
       </c>
       <c r="D79" t="s">
-        <v>355</v>
+        <v>410</v>
       </c>
       <c r="E79" t="s">
         <v>8</v>
@@ -8083,7 +8950,7 @@
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>356</v>
+        <v>411</v>
       </c>
       <c r="B80" t="s">
         <v>138</v>
@@ -8092,7 +8959,7 @@
         <v>171</v>
       </c>
       <c r="D80" t="s">
-        <v>310</v>
+        <v>365</v>
       </c>
       <c r="E80" t="s">
         <v>8</v>
@@ -8115,7 +8982,7 @@
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>357</v>
+        <v>412</v>
       </c>
       <c r="B81" t="s">
         <v>138</v>
@@ -8124,7 +8991,7 @@
         <v>166</v>
       </c>
       <c r="D81" t="s">
-        <v>290</v>
+        <v>345</v>
       </c>
       <c r="E81" t="s">
         <v>8</v>
@@ -8147,7 +9014,7 @@
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
-        <v>358</v>
+        <v>413</v>
       </c>
       <c r="B82" t="s">
         <v>138</v>
@@ -8156,7 +9023,7 @@
         <v>72</v>
       </c>
       <c r="D82" t="s">
-        <v>355</v>
+        <v>410</v>
       </c>
       <c r="E82" t="s">
         <v>8</v>
@@ -8179,10 +9046,10 @@
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>359</v>
+        <v>414</v>
       </c>
       <c r="B83" t="s">
-        <v>320</v>
+        <v>375</v>
       </c>
       <c r="C83" t="s">
         <v>8</v>
@@ -8197,7 +9064,7 @@
         <v>8</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>321</v>
+        <v>376</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -8211,7 +9078,7 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
-        <v>360</v>
+        <v>415</v>
       </c>
       <c r="B84" t="s">
         <v>138</v>
@@ -8220,7 +9087,7 @@
         <v>166</v>
       </c>
       <c r="D84" t="s">
-        <v>288</v>
+        <v>343</v>
       </c>
       <c r="E84" t="s">
         <v>8</v>
@@ -8243,7 +9110,7 @@
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>361</v>
+        <v>416</v>
       </c>
       <c r="B85" t="s">
         <v>138</v>
@@ -8252,7 +9119,7 @@
         <v>171</v>
       </c>
       <c r="D85" t="s">
-        <v>310</v>
+        <v>365</v>
       </c>
       <c r="E85" t="s">
         <v>8</v>
@@ -8275,7 +9142,7 @@
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
-        <v>362</v>
+        <v>417</v>
       </c>
       <c r="B86" t="s">
         <v>138</v>
@@ -8284,7 +9151,7 @@
         <v>72</v>
       </c>
       <c r="D86" t="s">
-        <v>355</v>
+        <v>410</v>
       </c>
       <c r="E86" t="s">
         <v>8</v>
@@ -8307,7 +9174,7 @@
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
-        <v>363</v>
+        <v>418</v>
       </c>
       <c r="B87" t="s">
         <v>138</v>
@@ -8316,7 +9183,7 @@
         <v>166</v>
       </c>
       <c r="D87" t="s">
-        <v>290</v>
+        <v>345</v>
       </c>
       <c r="E87" t="s">
         <v>8</v>
@@ -8339,7 +9206,7 @@
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
-        <v>364</v>
+        <v>419</v>
       </c>
       <c r="B88" t="s">
         <v>138</v>
@@ -8348,7 +9215,7 @@
         <v>44</v>
       </c>
       <c r="D88" t="s">
-        <v>284</v>
+        <v>339</v>
       </c>
       <c r="E88" t="s">
         <v>8</v>
@@ -8371,7 +9238,7 @@
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
-        <v>365</v>
+        <v>420</v>
       </c>
       <c r="B89" t="s">
         <v>138</v>
@@ -8380,7 +9247,7 @@
         <v>166</v>
       </c>
       <c r="D89" t="s">
-        <v>290</v>
+        <v>345</v>
       </c>
       <c r="E89" t="s">
         <v>8</v>
@@ -8403,7 +9270,7 @@
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
-        <v>366</v>
+        <v>421</v>
       </c>
       <c r="B90" t="s">
         <v>138</v>
@@ -8412,7 +9279,7 @@
         <v>44</v>
       </c>
       <c r="D90" t="s">
-        <v>284</v>
+        <v>339</v>
       </c>
       <c r="E90" t="s">
         <v>8</v>
@@ -8435,7 +9302,7 @@
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>367</v>
+        <v>422</v>
       </c>
       <c r="B91" t="s">
         <v>138</v>
@@ -8444,7 +9311,7 @@
         <v>166</v>
       </c>
       <c r="D91" t="s">
-        <v>290</v>
+        <v>345</v>
       </c>
       <c r="E91" t="s">
         <v>8</v>
@@ -8467,7 +9334,7 @@
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="s">
-        <v>368</v>
+        <v>423</v>
       </c>
       <c r="B92" t="s">
         <v>138</v>
@@ -8476,7 +9343,7 @@
         <v>44</v>
       </c>
       <c r="D92" t="s">
-        <v>284</v>
+        <v>339</v>
       </c>
       <c r="E92" t="s">
         <v>8</v>
@@ -8499,7 +9366,7 @@
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
-        <v>369</v>
+        <v>424</v>
       </c>
       <c r="B93" t="s">
         <v>138</v>
@@ -8508,7 +9375,7 @@
         <v>44</v>
       </c>
       <c r="D93" t="s">
-        <v>282</v>
+        <v>337</v>
       </c>
       <c r="E93" t="s">
         <v>8</v>
@@ -8531,7 +9398,7 @@
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="s">
-        <v>370</v>
+        <v>425</v>
       </c>
       <c r="B94" t="s">
         <v>138</v>
@@ -8540,7 +9407,7 @@
         <v>166</v>
       </c>
       <c r="D94" t="s">
-        <v>288</v>
+        <v>343</v>
       </c>
       <c r="E94" t="s">
         <v>8</v>
@@ -8563,10 +9430,10 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
-        <v>371</v>
+        <v>426</v>
       </c>
       <c r="B95" t="s">
-        <v>320</v>
+        <v>375</v>
       </c>
       <c r="C95" t="s">
         <v>8</v>
@@ -8581,7 +9448,7 @@
         <v>8</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>321</v>
+        <v>376</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -8595,7 +9462,7 @@
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
-        <v>372</v>
+        <v>427</v>
       </c>
       <c r="B96" t="s">
         <v>138</v>
@@ -8604,7 +9471,7 @@
         <v>72</v>
       </c>
       <c r="D96" t="s">
-        <v>373</v>
+        <v>428</v>
       </c>
       <c r="E96" t="s">
         <v>8</v>
@@ -8627,7 +9494,7 @@
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
-        <v>374</v>
+        <v>429</v>
       </c>
       <c r="B97" t="s">
         <v>138</v>
@@ -8636,7 +9503,7 @@
         <v>44</v>
       </c>
       <c r="D97" t="s">
-        <v>282</v>
+        <v>337</v>
       </c>
       <c r="E97" t="s">
         <v>8</v>
@@ -8659,7 +9526,7 @@
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
-        <v>375</v>
+        <v>430</v>
       </c>
       <c r="B98" t="s">
         <v>138</v>
@@ -8668,7 +9535,7 @@
         <v>166</v>
       </c>
       <c r="D98" t="s">
-        <v>288</v>
+        <v>343</v>
       </c>
       <c r="E98" t="s">
         <v>8</v>
@@ -8691,7 +9558,7 @@
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
-        <v>376</v>
+        <v>431</v>
       </c>
       <c r="B99" t="s">
         <v>138</v>
@@ -8700,7 +9567,7 @@
         <v>72</v>
       </c>
       <c r="D99" t="s">
-        <v>373</v>
+        <v>428</v>
       </c>
       <c r="E99" t="s">
         <v>8</v>
@@ -8723,10 +9590,10 @@
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
-        <v>377</v>
+        <v>432</v>
       </c>
       <c r="B100" t="s">
-        <v>320</v>
+        <v>375</v>
       </c>
       <c r="C100" t="s">
         <v>8</v>
@@ -8741,7 +9608,7 @@
         <v>8</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>378</v>
+        <v>433</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -8755,7 +9622,7 @@
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
-        <v>379</v>
+        <v>434</v>
       </c>
       <c r="B101" t="s">
         <v>138</v>
@@ -8764,7 +9631,7 @@
         <v>44</v>
       </c>
       <c r="D101" t="s">
-        <v>282</v>
+        <v>337</v>
       </c>
       <c r="E101" t="s">
         <v>8</v>
@@ -8787,7 +9654,7 @@
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
-        <v>380</v>
+        <v>435</v>
       </c>
       <c r="B102" t="s">
         <v>138</v>
@@ -8796,7 +9663,7 @@
         <v>166</v>
       </c>
       <c r="D102" t="s">
-        <v>288</v>
+        <v>343</v>
       </c>
       <c r="E102" t="s">
         <v>8</v>
@@ -8819,7 +9686,7 @@
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
-        <v>381</v>
+        <v>436</v>
       </c>
       <c r="B103" t="s">
         <v>138</v>
@@ -8828,7 +9695,7 @@
         <v>72</v>
       </c>
       <c r="D103" t="s">
-        <v>373</v>
+        <v>428</v>
       </c>
       <c r="E103" t="s">
         <v>8</v>
@@ -8851,7 +9718,7 @@
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
-        <v>382</v>
+        <v>437</v>
       </c>
       <c r="B104" t="s">
         <v>138</v>
@@ -8860,7 +9727,7 @@
         <v>171</v>
       </c>
       <c r="D104" t="s">
-        <v>310</v>
+        <v>365</v>
       </c>
       <c r="E104" t="s">
         <v>8</v>
@@ -8883,7 +9750,7 @@
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
-        <v>383</v>
+        <v>438</v>
       </c>
       <c r="B105" t="s">
         <v>138</v>
@@ -8892,7 +9759,7 @@
         <v>44</v>
       </c>
       <c r="D105" t="s">
-        <v>284</v>
+        <v>339</v>
       </c>
       <c r="E105" t="s">
         <v>8</v>
@@ -8915,7 +9782,7 @@
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
-        <v>384</v>
+        <v>439</v>
       </c>
       <c r="B106" t="s">
         <v>138</v>
@@ -8924,7 +9791,7 @@
         <v>171</v>
       </c>
       <c r="D106" t="s">
-        <v>310</v>
+        <v>365</v>
       </c>
       <c r="E106" t="s">
         <v>8</v>
@@ -8947,7 +9814,7 @@
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
-        <v>385</v>
+        <v>440</v>
       </c>
       <c r="B107" t="s">
         <v>138</v>
@@ -8956,7 +9823,7 @@
         <v>44</v>
       </c>
       <c r="D107" t="s">
-        <v>284</v>
+        <v>339</v>
       </c>
       <c r="E107" t="s">
         <v>8</v>
@@ -8979,7 +9846,7 @@
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" s="5" t="s">
-        <v>386</v>
+        <v>441</v>
       </c>
       <c r="B108" t="s">
         <v>138</v>
@@ -8988,7 +9855,7 @@
         <v>171</v>
       </c>
       <c r="D108" t="s">
-        <v>310</v>
+        <v>365</v>
       </c>
       <c r="E108" t="s">
         <v>8</v>
@@ -9011,7 +9878,7 @@
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="s">
-        <v>387</v>
+        <v>442</v>
       </c>
       <c r="B109" t="s">
         <v>138</v>
@@ -9020,7 +9887,7 @@
         <v>44</v>
       </c>
       <c r="D109" t="s">
-        <v>284</v>
+        <v>339</v>
       </c>
       <c r="E109" t="s">
         <v>8</v>

--- a/content/jahrgaenge/Jg7.xlsx
+++ b/content/jahrgaenge/Jg7.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2107" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2143" uniqueCount="474">
   <si>
     <t>Hinweise zu Jg7.xlsx</t>
   </si>
@@ -1349,6 +1349,99 @@
   </si>
   <si>
     <t>2027-05-27</t>
+  </si>
+  <si>
+    <t>jg7-r1</t>
+  </si>
+  <si>
+    <t>2026-08-17</t>
+  </si>
+  <si>
+    <t>Bausteinzeitraum 17.08. bis 11.09.2026</t>
+  </si>
+  <si>
+    <t>jg7-r2</t>
+  </si>
+  <si>
+    <t>Bausteinzeitraum 21.09. bis 30.10.2026</t>
+  </si>
+  <si>
+    <t>jg7-r3</t>
+  </si>
+  <si>
+    <t>2026-11-02</t>
+  </si>
+  <si>
+    <t>Bausteinzeitraum 02.11. bis 27.11.2026</t>
+  </si>
+  <si>
+    <t>jg7-r4</t>
+  </si>
+  <si>
+    <t>2026-11-30</t>
+  </si>
+  <si>
+    <t>2027-01-08</t>
+  </si>
+  <si>
+    <t>Bausteinzeitraum 30.11. bis 08.01.2027</t>
+  </si>
+  <si>
+    <t>jg7-r5</t>
+  </si>
+  <si>
+    <t>2027-01-11</t>
+  </si>
+  <si>
+    <t>Bausteinzeitraum 11.01. bis 05.02.2027</t>
+  </si>
+  <si>
+    <t>jg7-r6</t>
+  </si>
+  <si>
+    <t>2027-02-22</t>
+  </si>
+  <si>
+    <t>2027-03-19</t>
+  </si>
+  <si>
+    <t>Bausteinzeitraum 22.02. bis 19.03.2027</t>
+  </si>
+  <si>
+    <t>jg7-r7</t>
+  </si>
+  <si>
+    <t>2027-04-05</t>
+  </si>
+  <si>
+    <t>2027-04-30</t>
+  </si>
+  <si>
+    <t>Bausteinzeitraum 05.04. bis 30.04.2027</t>
+  </si>
+  <si>
+    <t>jg7-r8</t>
+  </si>
+  <si>
+    <t>2027-05-03</t>
+  </si>
+  <si>
+    <t>2027-06-04</t>
+  </si>
+  <si>
+    <t>Bausteinzeitraum 03.05. bis 04.06.2027</t>
+  </si>
+  <si>
+    <t>jg7-r9</t>
+  </si>
+  <si>
+    <t>2027-06-07</t>
+  </si>
+  <si>
+    <t>2027-07-02</t>
+  </si>
+  <si>
+    <t>Bausteinzeitraum 07.06. bis 02.07.2027</t>
   </si>
 </sst>
 </file>
@@ -2785,7 +2878,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2805,6 +2898,132 @@
       </c>
       <c r="D1" s="7" t="s">
         <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>443</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>446</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>448</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>451</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>455</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>458</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>462</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>466</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>470</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>471</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>473</v>
       </c>
     </row>
   </sheetData>
